--- a/templates/YesBank/YesBank_Collection_Template_2026-27.xlsx
+++ b/templates/YesBank/YesBank_Collection_Template_2026-27.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yes Bank\April 2026\Draft Reports - April 2026\Collection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachit Goyal\Downloads\audit-report-generator\templates\YesBank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC9CE74C-965E-4FA8-9CEF-320F2DE6BE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF1C5EA-E1DE-40C9-B84A-A71F92BFCE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{86A017A5-8E66-48E3-A3A0-AC94407BBF99}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E366AD21-7E7D-48B4-B5AD-0A6D4540711A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Rating" sheetId="2" r:id="rId1"/>
-    <sheet name="Agency" sheetId="3" r:id="rId2"/>
-    <sheet name="KAF" sheetId="4" r:id="rId3"/>
-    <sheet name="Annexure 1" sheetId="5" r:id="rId4"/>
-    <sheet name="Annexure 2" sheetId="6" r:id="rId5"/>
-    <sheet name="Anexure 3" sheetId="7" r:id="rId6"/>
-    <sheet name="Annexure-4" sheetId="8" r:id="rId7"/>
-    <sheet name="Annexure-5" sheetId="9" r:id="rId8"/>
+    <sheet name="Rating" sheetId="1" r:id="rId1"/>
+    <sheet name="Agency" sheetId="2" r:id="rId2"/>
+    <sheet name="KAF" sheetId="3" r:id="rId3"/>
+    <sheet name="Annexure 1" sheetId="4" r:id="rId4"/>
+    <sheet name="Annexure 2" sheetId="5" r:id="rId5"/>
+    <sheet name="Anexure 3" sheetId="6" r:id="rId6"/>
+    <sheet name="Annexure-4" sheetId="7" r:id="rId7"/>
+    <sheet name="Annexure-5" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Agency!$A$1:$O$69</definedName>
@@ -39,8 +39,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -48,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="314">
   <si>
     <t>YES Bank Collection Agency Audit</t>
   </si>
@@ -96,9 +94,6 @@
   </si>
   <si>
     <t>Products for which agency does collections</t>
-  </si>
-  <si>
-    <t>Retail Collection</t>
   </si>
   <si>
     <t>Agency person with whom the discussion were held</t>
@@ -273,25 +268,13 @@
     <t>Detailed observations needs to be updated here. And details of missing documents or any other pendency should be updated in the Annexure sheet</t>
   </si>
   <si>
-    <t>Yes, Compete vendor agreement is maintained at the agency</t>
-  </si>
-  <si>
     <t>2) If supplementary agreement the scope of work for Retails Collections needs to there.</t>
   </si>
   <si>
-    <t>Yes, Compete agreement is maintained at the agency</t>
-  </si>
-  <si>
     <t>3) Latest rate annexure</t>
   </si>
   <si>
-    <t>Yes, latest rate annexures maintained at the agency</t>
-  </si>
-  <si>
     <t>4) COC should be signed and displayed.</t>
-  </si>
-  <si>
-    <t>Yes, Code of Conduct poster is displayed at the agency</t>
   </si>
   <si>
     <t>BLUEBOOK</t>
@@ -310,9 +293,6 @@
     <t>Done: 10 else 2 for each such case</t>
   </si>
   <si>
-    <t>Blue book formats are filled completely/correctly by the agency</t>
-  </si>
-  <si>
     <t>2) Declaration cum undertaking page owners/CP signature should be filled up in blue book.</t>
   </si>
   <si>
@@ -331,9 +311,6 @@
     <t>7) Receipt book issuance register should be filled up properly and completely and should be matched with bank record.</t>
   </si>
   <si>
-    <t>Na as no physical receipt books are issued to the agency for the Audit period</t>
-  </si>
-  <si>
     <t>8) Agency training tracker should be filled up by CP/RCM if training has been provided.</t>
   </si>
   <si>
@@ -341,9 +318,6 @@
   </si>
   <si>
     <t>10) Repokit tracker should be filled up and matched with bank record applicable only for repo agency.</t>
-  </si>
-  <si>
-    <t>Na as no Repokit are issued to the agency for the Audit period</t>
   </si>
   <si>
     <t xml:space="preserve">Visitor Register </t>
@@ -391,9 +365,6 @@
   </si>
   <si>
     <t>Agencies / In-house team should deposit the collected payments in designated our Bank branches within 24 hours of collection.</t>
-  </si>
-  <si>
-    <t>NA as, During the audit review for the current quarter, it has been verified that no cash collection has been carried out by the designated agency</t>
   </si>
   <si>
     <t>Issuance</t>
@@ -407,24 +378,6 @@
 6.Whether all unused receipt books are in safe custody of agency's authorized person or not?</t>
   </si>
   <si>
-    <t>1.Please comment about the process of filling in the receipts (completely and correctly and without cuttings/alterations/ over writing on the receipts).</t>
-  </si>
-  <si>
-    <t>2.Do all cancelled receipts have all Four copies with the branch (Also check for hologram in cancelled receipts)?</t>
-  </si>
-  <si>
-    <t>3.Hologram needs to be tamperred on all cancelled and expired receipts.</t>
-  </si>
-  <si>
-    <t>4.Does the branch have FIR copies,indemnity bond  and newspaper advertisement cutout for  lost receipts ?</t>
-  </si>
-  <si>
-    <t>5.Whether the agencies managed by the Collection Partner (CP) have returned the expired/used receipt books as per process. Also applicable for the in-house books used by the Collection Partner (CP)</t>
-  </si>
-  <si>
-    <t>6.Whether all unused receipt books are in safe custody of agency's authorized person or not?</t>
-  </si>
-  <si>
     <t>ID CARD</t>
   </si>
   <si>
@@ -441,9 +394,6 @@
 non compliance</t>
   </si>
   <si>
-    <t>Yes, All Field Executives are DRA certified and hold valid digital ID cards issued by Yes Bank as per policy requirements.</t>
-  </si>
-  <si>
     <t>DRA</t>
   </si>
   <si>
@@ -456,13 +406,7 @@
     <t>Please take screenshots of all DRA certificate of Telecaller working for YBL.</t>
   </si>
   <si>
-    <t>Yes, All Callers employed by the agency are DRA certified in accordance with regulatory and institutional requirements.</t>
-  </si>
-  <si>
     <t>Whether all ID cards where executives have been resigned/terminated are submitted to CP/Central Processing Team and same has been updated in ID card tracker of bluebook or not?</t>
-  </si>
-  <si>
-    <t>NA as no Such case was observed for the audit period</t>
   </si>
   <si>
     <t>Sub-Total</t>
@@ -481,9 +425,6 @@
     <t>1) Auditor should do live checking of Y CAPS Allocation download at the time of audit.</t>
   </si>
   <si>
-    <t>Yes, the same has been compiled by the agency as per Bank Process</t>
-  </si>
-  <si>
     <t>2) Cross  tally allocation downloaded on caps with allocation available in system as well as allocation provided by Central team for audit purpose.</t>
   </si>
   <si>
@@ -510,9 +451,6 @@
     <t>Please do live checking related to trail updation and receipt making process.Screenshot of all FOS's Marc id is required.</t>
   </si>
   <si>
-    <t>Whether all the FOS has MCAPS ID’s and are active?</t>
-  </si>
-  <si>
     <t>Trails</t>
   </si>
   <si>
@@ -524,9 +462,6 @@
   </si>
   <si>
     <t xml:space="preserve">Pls impact score if trails uploaded is &lt;70% or PTP is &gt;=98% </t>
-  </si>
-  <si>
-    <t>Yes, Calling feedback and visit feedback are recorded by the agency for their allotted cases</t>
   </si>
   <si>
     <t>Trails Updation in Y CAPS</t>
@@ -573,9 +508,6 @@
     </r>
   </si>
   <si>
-    <t>Yes, Code of Conduct guidelines was followed by telecaller during the call to customer</t>
-  </si>
-  <si>
     <t>Call Recording Data</t>
   </si>
   <si>
@@ -588,25 +520,13 @@
     <t xml:space="preserve">Done : 10 else : -2 for each month </t>
   </si>
   <si>
-    <t>Yes, Call recording facility available at the agency &amp; 100% call recordings were done</t>
-  </si>
-  <si>
     <t>2) Live calling should be checked at the time of agency visit.</t>
   </si>
   <si>
-    <t>Yes, Live call recording facility available and working at the time of audit</t>
-  </si>
-  <si>
     <t>3 )Customers are contacted only between  8 am to 7 pm . In case of deviations same is to be highlighted in the audit observations</t>
   </si>
   <si>
-    <t>Yes, Calling was done by the agency as per COC guidelines</t>
-  </si>
-  <si>
     <t>4) Call intensity  to be checked for allocated cases.</t>
-  </si>
-  <si>
-    <t>Yes, Call intensity was followed by the agency as per COC guidelines</t>
   </si>
   <si>
     <t>Whether call recording data is maintained for minimum 12 months by the agencies ? Also, check whether agencies have back-up of the call recording data.
@@ -634,9 +554,6 @@
     </r>
   </si>
   <si>
-    <t>Yes, Call recording data are available with agency for 12 months</t>
-  </si>
-  <si>
     <t>TARGETSETTING LETTER</t>
   </si>
   <si>
@@ -652,13 +569,7 @@
     <t>Target setting letter of a particular month should be documented by 5th of same month.</t>
   </si>
   <si>
-    <t>Yes, Target setting letters are maintain by the agency as per Bank policy</t>
-  </si>
-  <si>
     <t>2) Please check agency sign and stamp along with CP sign on target letter.</t>
-  </si>
-  <si>
-    <t>Yes, Target setting letters are maintain by the agency with complete and correct details</t>
   </si>
   <si>
     <t>VENDOR PERFORMANCE REPORT</t>
@@ -687,12 +598,6 @@
     </r>
   </si>
   <si>
-    <t>Yes, monthly vendor performance are maintain by the agency as per Bank policy</t>
-  </si>
-  <si>
-    <t>Yes, monthly vendor performance are maintain by the agency with complete and correct details</t>
-  </si>
-  <si>
     <t>SYSTEM &amp; SECURITY</t>
   </si>
   <si>
@@ -709,9 +614,6 @@
   </si>
   <si>
     <t>USB/CD/floppy drive should not be active for data transfer</t>
-  </si>
-  <si>
-    <t>Yes, USB/CD/Floppy drive was inactive for data transfer at agency for allotted system</t>
   </si>
   <si>
     <t>Whether agency has purged data as per bank's policy ?</t>
@@ -815,454 +717,370 @@
     <t>Please check insurance validity date,agency name and address on insurance copy</t>
   </si>
   <si>
+    <t>SHOP ESTABLISHMENT CERTIFICATE</t>
+  </si>
+  <si>
+    <t>Agency establishment</t>
+  </si>
+  <si>
+    <t>Whether agencies have shop establishment certificate ?IF not check Declaration.</t>
+  </si>
+  <si>
+    <t>Please check agency name and address mentioned on shop establishment copy.</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>INFRASTRUCTURE &amp; OTHER</t>
+  </si>
+  <si>
+    <t>our bank's reference made on co's name board</t>
+  </si>
+  <si>
+    <t>Has the agency made any reference to our Bank's name on the company's name board.?</t>
+  </si>
+  <si>
+    <t>Pls also check whether the Infrastructure like PC / Laptop , document storage, FOS etc. are used exclusively for our Bank &amp; not mixed with others.</t>
+  </si>
+  <si>
+    <t>Agency details update in ERP</t>
+  </si>
+  <si>
+    <t>Whether agency's address &amp; phone number are correctly updated on YES BANK website.Www.yesbank.in/regulatory_policies</t>
+  </si>
+  <si>
+    <t>Auditor to check on the web site and confirm .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bill </t>
+  </si>
+  <si>
+    <t>Whether Copy of Monthly bill is available at agency? Is There Any Pending Bill ? (If Yes Mention Details).Billing to be checked as per pickup and collection agency payment Grid</t>
+  </si>
+  <si>
+    <t>As per the Grid pickup and collection agency needs to be paid separetly</t>
+  </si>
+  <si>
+    <t>No Dues Certificate related</t>
+  </si>
+  <si>
+    <t>Whether NDC is provided by the agency for previous quarter bills that have been paid?Copy of NDC to be maintained with the agency</t>
+  </si>
+  <si>
+    <t>As per process agency is required to give "No due certificate" for payout given to agency.</t>
+  </si>
+  <si>
+    <t>Not cooperated with Auditor</t>
+  </si>
+  <si>
+    <t>Whether full cooperation/complete &amp; timely data was received from agency for completing audit?</t>
+  </si>
+  <si>
+    <t>Pls impact score if the agency pre-scheduled  &amp; intimated is cancelled on the day / a day before visit.</t>
+  </si>
+  <si>
+    <t>Non compliance of last month's audit observation.</t>
+  </si>
+  <si>
+    <t>Whether non-compliance reported in the previous period adhered to?</t>
+  </si>
+  <si>
+    <t>As per audit observation</t>
+  </si>
+  <si>
+    <t>Additional point</t>
+  </si>
+  <si>
+    <t>Any other comment which Auditor wants to give</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Main Category</t>
+  </si>
+  <si>
+    <t>Check Points Category</t>
+  </si>
+  <si>
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>Sub Remarks</t>
+  </si>
+  <si>
+    <t>Loan Account No.</t>
+  </si>
+  <si>
+    <t>Customer Name</t>
+  </si>
+  <si>
+    <t>Vendor Name</t>
+  </si>
+  <si>
+    <t>Executive Name</t>
+  </si>
+  <si>
+    <t>ID Card No.</t>
+  </si>
+  <si>
+    <t>Repo-Kit No.</t>
+  </si>
+  <si>
+    <t>Repo Date</t>
+  </si>
+  <si>
+    <t>Godown Name</t>
+  </si>
+  <si>
+    <t>Godown Location</t>
+  </si>
+  <si>
+    <t>Sale / Release Date</t>
+  </si>
+  <si>
+    <t>Sale / Release Amount</t>
+  </si>
+  <si>
+    <t>Category Of Mismatch</t>
+  </si>
+  <si>
+    <t>Mismatch Details</t>
+  </si>
+  <si>
+    <t>Repokit Return Date</t>
+  </si>
+  <si>
+    <t>Valuation Dt -Valuation Report</t>
+  </si>
+  <si>
+    <t>Valuation Date-Yards Register</t>
+  </si>
+  <si>
+    <t>Type Of Executive</t>
+  </si>
+  <si>
+    <t>Rcu Positive (Yes/No)</t>
+  </si>
+  <si>
+    <t>Dra Trained (Yes/No/Na)</t>
+  </si>
+  <si>
+    <t>Annexure To Form Part Of Agency Report :</t>
+  </si>
+  <si>
+    <t>Sr No</t>
+  </si>
+  <si>
+    <t>Name of FOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ID Card No</t>
+  </si>
+  <si>
+    <t>Source of information (Telephonic/ Personal Interaction)</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Trained on code of conduct</t>
+  </si>
+  <si>
+    <t>Holding valid id card</t>
+  </si>
+  <si>
+    <t>Remark</t>
+  </si>
+  <si>
+    <t>Annexure :Call Recording Sampling Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                        </t>
+  </si>
+  <si>
+    <t>LAN</t>
+  </si>
+  <si>
+    <t>Call Recording available (Y/N)</t>
+  </si>
+  <si>
+    <t>REMARKS</t>
+  </si>
+  <si>
+    <t>Annexure : Receipt Recording Status</t>
+  </si>
+  <si>
+    <t>SR. No</t>
+  </si>
+  <si>
+    <t>Receipt no.</t>
+  </si>
+  <si>
+    <t>Updated in Y CAPS(Yes/No)</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NA, No such cases were found during audit period.</t>
+  </si>
+  <si>
+    <t>Annexure : Call Recording Count</t>
+  </si>
+  <si>
+    <t>January'26</t>
+  </si>
+  <si>
+    <t>Februay'26</t>
+  </si>
+  <si>
+    <t>March'26</t>
+  </si>
+  <si>
+    <t>Non ID Card Allocation Details :</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>CP Name</t>
+  </si>
+  <si>
+    <t>Non ID Card Executive name</t>
+  </si>
+  <si>
+    <t>Whether all the FOS has MCAPS ID’s and are active?</t>
+  </si>
+  <si>
+    <t>1.Please comment about the process of filling in the receipts (completely and correctly and without cuttings/alterations/ over writing on the receipts).</t>
+  </si>
+  <si>
+    <t>2.Do all cancelled receipts have all Four copies with the branch (Also check for hologram in cancelled receipts)?</t>
+  </si>
+  <si>
+    <t>3.Hologram needs to be tamperred on all cancelled and expired receipts.</t>
+  </si>
+  <si>
+    <t>4.Does the branch have FIR copies,indemnity bond  and newspaper advertisement cutout for  lost receipts ?</t>
+  </si>
+  <si>
+    <t>5.Whether the agencies managed by the Collection Partner (CP) have returned the expired/used receipt books as per process. Also applicable for the in-house books used by the Collection Partner (CP)</t>
+  </si>
+  <si>
+    <t>6.Whether all unused receipt books are in safe custody of agency's authorized person or not?</t>
+  </si>
+  <si>
+    <t>Retail Collection</t>
+  </si>
+  <si>
+    <t>NA as, During the audit review for the current quarter, it has been verified that no cash collection has been carried out by the designated agency</t>
+  </si>
+  <si>
+    <t>Yes, the same has been compiled by the agency as per Bank Process</t>
+  </si>
+  <si>
+    <t>Na as no physical receipt books are issued to the agency for the Audit period</t>
+  </si>
+  <si>
+    <t>Yes, All Field Executives are DRA certified and hold valid digital ID cards issued by Yes Bank as per policy requirements.</t>
+  </si>
+  <si>
+    <t>Yes, All Callers employed by the agency are DRA certified in accordance with regulatory and institutional requirements.</t>
+  </si>
+  <si>
+    <t>NA as no Such case was observed for the audit period</t>
+  </si>
+  <si>
+    <t>Yes, Call recording data are available with agency for 12 months</t>
+  </si>
+  <si>
+    <t>Yes, Target setting letters are maintain by the agency as per Bank policy</t>
+  </si>
+  <si>
+    <t>Yes, monthly vendor performance are maintain by the agency as per Bank policy</t>
+  </si>
+  <si>
+    <t>Yes, USB/CD/Floppy drive was inactive for data transfer at agency for allotted system</t>
+  </si>
+  <si>
     <t>Yes, Valid Fidelity insurance(cash in transit &amp; cash in safe) is available at the Agency</t>
   </si>
   <si>
-    <t>SHOP ESTABLISHMENT CERTIFICATE</t>
-  </si>
-  <si>
-    <t>Agency establishment</t>
-  </si>
-  <si>
-    <t>Whether agencies have shop establishment certificate ?IF not check Declaration.</t>
-  </si>
-  <si>
-    <t>Please check agency name and address mentioned on shop establishment copy.</t>
-  </si>
-  <si>
     <t>Yes, Shop establishment certificate is available with agency</t>
   </si>
   <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>INFRASTRUCTURE &amp; OTHER</t>
-  </si>
-  <si>
-    <t>our bank's reference made on co's name board</t>
-  </si>
-  <si>
-    <t>Has the agency made any reference to our Bank's name on the company's name board.?</t>
-  </si>
-  <si>
-    <t>Pls also check whether the Infrastructure like PC / Laptop , document storage, FOS etc. are used exclusively for our Bank &amp; not mixed with others.</t>
-  </si>
-  <si>
-    <t>Agency details update in ERP</t>
-  </si>
-  <si>
-    <t>Whether agency's address &amp; phone number are correctly updated on YES BANK website.Www.yesbank.in/regulatory_policies</t>
-  </si>
-  <si>
-    <t>Auditor to check on the web site and confirm .</t>
-  </si>
-  <si>
     <t>Yes, agency's address &amp; phone number are correctly updated on Yes Bank web site</t>
   </si>
   <si>
-    <t xml:space="preserve">Bill </t>
-  </si>
-  <si>
-    <t>Whether Copy of Monthly bill is available at agency? Is There Any Pending Bill ? (If Yes Mention Details).Billing to be checked as per pickup and collection agency payment Grid</t>
-  </si>
-  <si>
-    <t>As per the Grid pickup and collection agency needs to be paid separetly</t>
-  </si>
-  <si>
     <t>Yes, Copy of Monthly bill is available at agency</t>
   </si>
   <si>
-    <t>No Dues Certificate related</t>
-  </si>
-  <si>
-    <t>Whether NDC is provided by the agency for previous quarter bills that have been paid?Copy of NDC to be maintained with the agency</t>
-  </si>
-  <si>
-    <t>As per process agency is required to give "No due certificate" for payout given to agency.</t>
-  </si>
-  <si>
     <t>Yes, NDC for the Last quarter is available at agency</t>
   </si>
   <si>
-    <t>Not cooperated with Auditor</t>
-  </si>
-  <si>
-    <t>Whether full cooperation/complete &amp; timely data was received from agency for completing audit?</t>
-  </si>
-  <si>
-    <t>Pls impact score if the agency pre-scheduled  &amp; intimated is cancelled on the day / a day before visit.</t>
-  </si>
-  <si>
     <t>Yes, Full cooperation/complete &amp; timely data was received from agency for completing the audit</t>
   </si>
   <si>
-    <t>Non compliance of last month's audit observation.</t>
-  </si>
-  <si>
-    <t>Whether non-compliance reported in the previous period adhered to?</t>
-  </si>
-  <si>
-    <t>As per audit observation</t>
-  </si>
-  <si>
     <t>Yes, non-compliance reported in the previous period are rectified and not observed for the current audit period</t>
   </si>
   <si>
-    <t>Additional point</t>
-  </si>
-  <si>
-    <t>Any other comment which Auditor wants to give</t>
-  </si>
-  <si>
     <t>No comment, No Additional case/observation was observed for the audit period</t>
   </si>
   <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>Main Category</t>
-  </si>
-  <si>
-    <t>Check Points Category</t>
-  </si>
-  <si>
-    <t>Zone</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Employee ID</t>
-  </si>
-  <si>
-    <t>Sub Remarks</t>
-  </si>
-  <si>
-    <t>Loan Account No.</t>
-  </si>
-  <si>
-    <t>Customer Name</t>
-  </si>
-  <si>
-    <t>Vendor Name</t>
-  </si>
-  <si>
-    <t>Executive Name</t>
-  </si>
-  <si>
-    <t>ID Card No.</t>
-  </si>
-  <si>
-    <t>Repo-Kit No.</t>
-  </si>
-  <si>
-    <t>Repo Date</t>
-  </si>
-  <si>
-    <t>Godown Name</t>
-  </si>
-  <si>
-    <t>Godown Location</t>
-  </si>
-  <si>
-    <t>Sale / Release Date</t>
-  </si>
-  <si>
-    <t>Sale / Release Amount</t>
-  </si>
-  <si>
-    <t>Category Of Mismatch</t>
-  </si>
-  <si>
-    <t>Mismatch Details</t>
-  </si>
-  <si>
-    <t>Repokit Return Date</t>
-  </si>
-  <si>
-    <t>Valuation Dt -Valuation Report</t>
-  </si>
-  <si>
-    <t>Valuation Date-Yards Register</t>
-  </si>
-  <si>
-    <t>Type Of Executive</t>
-  </si>
-  <si>
-    <t>Rcu Positive (Yes/No)</t>
-  </si>
-  <si>
-    <t>Dra Trained (Yes/No/Na)</t>
-  </si>
-  <si>
-    <t>Annexure To Form Part Of Agency Report :</t>
-  </si>
-  <si>
-    <t>Sr No</t>
-  </si>
-  <si>
-    <t>Name of FOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ID Card No</t>
-  </si>
-  <si>
-    <t>Source of information (Telephonic/ Personal Interaction)</t>
-  </si>
-  <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>Trained on code of conduct</t>
-  </si>
-  <si>
-    <t>Holding valid id card</t>
-  </si>
-  <si>
-    <t>Remark</t>
-  </si>
-  <si>
-    <t>Annexure :Call Recording Sampling Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                        </t>
-  </si>
-  <si>
-    <t>LAN</t>
-  </si>
-  <si>
-    <t>Call Recording available (Y/N)</t>
-  </si>
-  <si>
-    <t>REMARKS</t>
-  </si>
-  <si>
-    <t>Annexure : Receipt Recording Status</t>
-  </si>
-  <si>
-    <t>SR. No</t>
-  </si>
-  <si>
-    <t>Receipt no.</t>
-  </si>
-  <si>
-    <t>Updated in Y CAPS(Yes/No)</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NA, No such cases were found during audit period.</t>
-  </si>
-  <si>
-    <t>Annexure : Call Recording Count</t>
-  </si>
-  <si>
-    <t>January'26</t>
-  </si>
-  <si>
-    <t>Februay'26</t>
-  </si>
-  <si>
-    <t>March'26</t>
-  </si>
-  <si>
-    <t>Non ID Card Allocation Details :</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>CP Name</t>
-  </si>
-  <si>
-    <t>Non ID Card Executive name</t>
-  </si>
-  <si>
-    <t>January 2026 to March 2026</t>
-  </si>
-  <si>
-    <t>Kumar Gaurav Agarwal and Company</t>
-  </si>
-  <si>
-    <t>Chandigarh</t>
-  </si>
-  <si>
-    <t>Aman Monga / 9990034588</t>
-  </si>
-  <si>
-    <t>Saksham Enterprises</t>
-  </si>
-  <si>
-    <t>Parveen Kumar, Gaurav Mahajan, Maninder Kumar</t>
-  </si>
-  <si>
-    <t>PKE6446010, GME5833008, MKE6407056, MKE6407067</t>
-  </si>
-  <si>
-    <t>Sanjeev Kumar, Vineet Kumar, Sameer Dhar, Ashutosh Gupta</t>
-  </si>
-  <si>
-    <t>Surjit</t>
-  </si>
-  <si>
-    <t>Scf - 3, Second Floor, Bhainsa Tibba, Sector 4  Mansa Devi Complex, Above Bansal Kulcha. ,I.T.Park Road, Panchkula - 134114</t>
-  </si>
-  <si>
-    <t>Yes the same has been complied by the agency</t>
-  </si>
-  <si>
-    <t>ALN</t>
-  </si>
-  <si>
-    <t>ALN012001831890</t>
-  </si>
-  <si>
-    <t>AASHISH  MISHRA</t>
-  </si>
-  <si>
-    <t>UCL</t>
-  </si>
-  <si>
-    <t>UCL011001884916</t>
-  </si>
-  <si>
-    <t>VARUN  SHARMA</t>
-  </si>
-  <si>
-    <t>UCL011001884930</t>
-  </si>
-  <si>
-    <t>UCL089100831248</t>
-  </si>
-  <si>
-    <t>RAMANDEEP SINGH</t>
-  </si>
-  <si>
-    <t>ALN020701006281</t>
-  </si>
-  <si>
-    <t>GAGANPREET KAUR</t>
-  </si>
-  <si>
-    <t>ALN020701011243</t>
-  </si>
-  <si>
-    <t>MANPREET KAUR</t>
-  </si>
-  <si>
-    <t>ALN020701084876</t>
-  </si>
-  <si>
-    <t>HARPAL SINGH</t>
-  </si>
-  <si>
-    <t>UCL012001589241</t>
-  </si>
-  <si>
-    <t>RAKESH KUMAR</t>
-  </si>
-  <si>
-    <t>UCL085702084570</t>
-  </si>
-  <si>
-    <t>SUKHWINDER  SINGH</t>
-  </si>
-  <si>
-    <t>UCL012001586936</t>
-  </si>
-  <si>
-    <t>ARUN KUMAR</t>
-  </si>
-  <si>
-    <t>ALN020701322961</t>
-  </si>
-  <si>
-    <t>GURJIT SINGH</t>
-  </si>
-  <si>
-    <t>UCL089101847082</t>
-  </si>
-  <si>
-    <t>RAVINDER  SINGH</t>
-  </si>
-  <si>
-    <t>No Deviation</t>
-  </si>
-  <si>
-    <t>SATINDER SINGH</t>
-  </si>
-  <si>
-    <t>C121902022</t>
-  </si>
-  <si>
-    <t>Not Verified</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>SURJIT SINGH</t>
-  </si>
-  <si>
-    <t>C121902026</t>
-  </si>
-  <si>
-    <t>JATINDER SINGH</t>
-  </si>
-  <si>
-    <t>C032002517</t>
-  </si>
-  <si>
-    <t>ROHIT THAKUR</t>
-  </si>
-  <si>
-    <t>C032002562</t>
-  </si>
-  <si>
-    <t>Personal Interaction</t>
-  </si>
-  <si>
-    <t>RAVINDER SINGH</t>
-  </si>
-  <si>
-    <t>C032003286</t>
-  </si>
-  <si>
-    <t>DAVINDER KUMAR</t>
-  </si>
-  <si>
-    <t>C042400396</t>
-  </si>
-  <si>
-    <t>PARTAP SINGH</t>
-  </si>
-  <si>
-    <t>C082400929</t>
-  </si>
-  <si>
-    <t>ANIL KUMAR</t>
-  </si>
-  <si>
-    <t>C032500242</t>
-  </si>
-  <si>
-    <t>ANKIT CHOPRA</t>
-  </si>
-  <si>
-    <t>C062500565</t>
-  </si>
-  <si>
-    <t>SONU KUMAR</t>
-  </si>
-  <si>
-    <t>C012601284</t>
+    <t>Yes, latest rate annexures maintained at the agency</t>
+  </si>
+  <si>
+    <t>Yes, Code of Conduct poster is displayed at the agency</t>
+  </si>
+  <si>
+    <t>Yes, Compete vendor agreement is maintained at the agency</t>
+  </si>
+  <si>
+    <t>Yes, Compete agreement is maintained at the agency</t>
+  </si>
+  <si>
+    <t>Yes, Calling feedback and visit feedback are recorded by the agency for their allotted cases</t>
+  </si>
+  <si>
+    <t>Na as no Repokit are issued to the agency for the Audit period</t>
+  </si>
+  <si>
+    <t>Yes, Call recording facility available at the agency &amp; 100% call recordings were done</t>
+  </si>
+  <si>
+    <t>Yes, Live call recording facility available and working at the time of audit</t>
+  </si>
+  <si>
+    <t>Yes, Target setting letters are maintain by the agency with complete and correct details</t>
+  </si>
+  <si>
+    <t>Yes, monthly vendor performance are maintain by the agency with complete and correct details</t>
+  </si>
+  <si>
+    <t>Blue book formats are filled completely/correctly by the agency</t>
+  </si>
+  <si>
+    <t>Yes, Code of Conduct guidelines was followed by telecaller during the call to customer</t>
+  </si>
+  <si>
+    <t>Yes, Calling was done by the agency as per COC guidelines</t>
+  </si>
+  <si>
+    <t>Yes, Call intensity was followed by the agency as per COC guidelines</t>
+  </si>
+  <si>
+    <t>KGAC</t>
   </si>
 </sst>
 </file>
@@ -1276,12 +1094,6 @@
     <numFmt numFmtId="167" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="27" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="2"/>
-    </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1390,6 +1202,12 @@
       <sz val="9"/>
       <name val="Book Antiqua"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1701,520 +1519,511 @@
   </borders>
   <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="19" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="19" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="19" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="9" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="9" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="9" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="9" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="9" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="9" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="9" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="9" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="9" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="9" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="9" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="9" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="24" fillId="0" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="24" fillId="0" borderId="12" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
-    <cellStyle name="_Amar's Vehicle_Audit_Report_auto_july_agt_06_Nasik Auto Jan. 07_cv_PIVOT 1_SERIES 2" xfId="7" xr:uid="{D38F0D64-4866-4B4D-B59E-CD992EB67C84}"/>
-    <cellStyle name="DataPilot Category" xfId="2" xr:uid="{6A41FA43-33DB-411E-84F7-C1AF9836DB7D}"/>
-    <cellStyle name="Good 2" xfId="3" xr:uid="{9EEB7729-1A6B-4512-8041-CD783B2CA6E5}"/>
+    <cellStyle name="_Amar's Vehicle_Audit_Report_auto_july_agt_06_Nasik Auto Jan. 07_cv_PIVOT 1_SERIES 2" xfId="7" xr:uid="{80A8BD56-6ED2-42AB-AA86-B312A219BC06}"/>
+    <cellStyle name="_Budg based on trend 1_CPC-RPC BSC SEPT-06_Book6_Branch_Metrics_CPA_Final_APR 09  BM UPLOAD_2" xfId="6" xr:uid="{28E173ED-E52B-43E0-9A01-6200B33124B0}"/>
+    <cellStyle name="DataPilot Category" xfId="3" xr:uid="{C2EC733E-5CFA-407E-B51E-3AC609C5D00F}"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 12" xfId="9" xr:uid="{C00F3DE5-FA73-4256-8166-7FFB06135D45}"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{3A2BC50A-6F6C-461C-9877-38B60263332F}"/>
-    <cellStyle name="Normal 2 2" xfId="6" xr:uid="{5EF2E20A-1FD7-40B2-B70E-EB6BA28FCDE2}"/>
-    <cellStyle name="Normal 3" xfId="10" xr:uid="{B7657DF7-5192-4A82-8C8B-8EB6F2FEAEFC}"/>
-    <cellStyle name="Normal_DM_1" xfId="5" xr:uid="{345D20EA-1E50-46C3-A65F-71BC1442B1AE}"/>
-    <cellStyle name="Normal_Sheet1" xfId="8" xr:uid="{2EF02DA0-3A35-41DE-A18B-A86F1C464384}"/>
-    <cellStyle name="Percent 2" xfId="4" xr:uid="{E1A7E795-7470-48B1-B6B8-77D899BF4001}"/>
+    <cellStyle name="Normal 12" xfId="9" xr:uid="{FFDD31A4-3149-42E5-96DD-6A6E1E53F612}"/>
+    <cellStyle name="Normal 2" xfId="5" xr:uid="{A6F519D4-B5BB-4C5C-BDDC-95796F400E88}"/>
+    <cellStyle name="Normal 3" xfId="10" xr:uid="{42B7EA57-F015-484E-8E89-09920FFF5840}"/>
+    <cellStyle name="Normal_DM_1" xfId="4" xr:uid="{47B18B6C-E73C-4527-9963-C930DB66557B}"/>
+    <cellStyle name="Normal_Sheet1" xfId="8" xr:uid="{09FDA902-1D9B-48A7-B13B-EDDE10EE22BC}"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2556,34 +2365,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF970CE0-47A4-4B22-9B4E-AAFC1AFCC0C8}">
-  <sheetPr codeName="Sheet2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AAB682D-8C31-499F-9FB4-3DECD3A3C123}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:K33"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="40.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="60.75" style="1" customWidth="1"/>
-    <col min="8" max="11" width="6.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8" style="1"/>
+    <col min="1" max="1" width="1.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="69.44140625" style="1" customWidth="1"/>
+    <col min="8" max="11" width="7.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="14.25" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="147" t="s">
+    <row r="1" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="144" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="148"/>
-      <c r="D2" s="148"/>
-      <c r="E2" s="148"/>
-      <c r="F2" s="148"/>
-      <c r="G2" s="149"/>
-    </row>
-    <row r="5" spans="2:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="146"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -2592,105 +2401,83 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="2:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>317</v>
-      </c>
+      <c r="C6" s="3"/>
       <c r="D6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>315</v>
-      </c>
+      <c r="E6" s="3"/>
       <c r="F6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>322</v>
-      </c>
+      <c r="G6" s="3"/>
       <c r="H6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="5">
-        <v>46136</v>
-      </c>
+      <c r="C7" s="5"/>
       <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>313</v>
-      </c>
+      <c r="E7" s="3"/>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>318</v>
-      </c>
+      <c r="C8" s="3"/>
       <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>320</v>
-      </c>
+      <c r="E8" s="3"/>
       <c r="F8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>316</v>
-      </c>
+      <c r="G8" s="3"/>
       <c r="H8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>319</v>
-      </c>
+      <c r="C9" s="3"/>
       <c r="D9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="2:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>321</v>
-      </c>
+      <c r="E10" s="3"/>
       <c r="F10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2698,7 +2485,7 @@
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2706,9 +2493,9 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2720,21 +2507,21 @@
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
     </row>
-    <row r="14" spans="2:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="B14" s="150" t="s">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="147" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="144" t="s">
+      <c r="D14" s="141" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="144" t="s">
+      <c r="E14" s="141" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="144" t="s">
+      <c r="F14" s="141" t="s">
         <v>22</v>
-      </c>
-      <c r="F14" s="144" t="s">
-        <v>23</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
@@ -2742,21 +2529,21 @@
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
     </row>
-    <row r="15" spans="2:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="B15" s="151"/>
-      <c r="C15" s="145"/>
-      <c r="D15" s="145"/>
-      <c r="E15" s="145"/>
-      <c r="F15" s="145"/>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="148"/>
+      <c r="C15" s="142"/>
+      <c r="D15" s="142"/>
+      <c r="E15" s="142"/>
+      <c r="F15" s="142"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
-    <row r="16" spans="2:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" s="13">
         <f>Agency!J29</f>
@@ -2771,9 +2558,9 @@
       </c>
       <c r="F16" s="15"/>
     </row>
-    <row r="17" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" s="13">
         <f>Agency!J47</f>
@@ -2788,9 +2575,9 @@
       </c>
       <c r="F17" s="15"/>
     </row>
-    <row r="18" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" s="13">
         <f>Agency!J58</f>
@@ -2805,9 +2592,9 @@
       </c>
       <c r="F18" s="15"/>
     </row>
-    <row r="19" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" s="13">
         <f>Agency!J61</f>
@@ -2822,9 +2609,9 @@
       </c>
       <c r="F19" s="15"/>
     </row>
-    <row r="20" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" s="13">
         <f>Agency!J69</f>
@@ -2839,9 +2626,9 @@
       </c>
       <c r="F20" s="15"/>
     </row>
-    <row r="21" spans="2:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C21" s="16">
         <f>SUM(C16:C20)</f>
@@ -2855,108 +2642,105 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F21" s="144" t="str">
+      <c r="F21" s="141" t="str">
         <f>IF(ROUNDUP(E21,2)&lt;60%,"C",IF(ROUNDUP(E21,2)&lt;70%,"C+",IF(ROUNDUP(E21,2)&lt;80%,"B",IF(ROUNDUP(E21,2)&lt;90%,"B+",IF(ROUNDUP(E21,2)&lt;100%,"A","A+")))))</f>
         <v>A+</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="146" t="str">
+        <v>29</v>
+      </c>
+      <c r="C22" s="143" t="str">
         <f>VLOOKUP($F$21,$C$27:$D$33,2,FALSE)</f>
         <v>Excellent</v>
       </c>
-      <c r="D22" s="146"/>
-      <c r="E22" s="146"/>
-      <c r="F22" s="145"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E24" s="143"/>
-    </row>
-    <row r="26" spans="2:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="D22" s="143"/>
+      <c r="E22" s="143"/>
+      <c r="F22" s="142"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="20"/>
     </row>
-    <row r="27" spans="2:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="22">
         <v>100</v>
       </c>
       <c r="C28" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="D28" s="24" t="s">
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="24" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="24" t="s">
+      <c r="C29" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="D29" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="24" t="s">
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="24" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="24" t="s">
+      <c r="C30" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="D30" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="24" t="s">
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="24" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="24" t="s">
+      <c r="C31" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="D31" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="24" t="s">
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="24" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="24" t="s">
+      <c r="C32" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="D32" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="24" t="s">
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B33" s="24" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="24" t="s">
+      <c r="C33" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="D33" s="24" t="s">
         <v>49</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2976,271 +2760,271 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E509BF75-0CD9-4225-88A8-408C21FB149C}">
-  <sheetPr codeName="Sheet3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFF79A9-AAFD-4D81-A36D-D1E2C7B7DE92}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:O69"/>
-  <sheetFormatPr defaultColWidth="18.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="21.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" style="97" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.875" style="70" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.875" style="46" customWidth="1"/>
-    <col min="4" max="4" width="8.625" style="98" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.875" style="46" customWidth="1"/>
-    <col min="6" max="6" width="37.375" style="46" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="46" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.625" style="46" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10" style="46" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.375" style="46" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.125" style="46" customWidth="1"/>
-    <col min="12" max="12" width="42.875" style="46" customWidth="1"/>
-    <col min="13" max="13" width="18.25" style="46" customWidth="1"/>
-    <col min="14" max="14" width="18.875" style="46" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.875" style="46" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="18.875" style="46"/>
+    <col min="1" max="1" width="9.109375" style="97" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="70" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" style="47" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" style="98" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.5546875" style="47" customWidth="1"/>
+    <col min="6" max="6" width="42.6640625" style="47" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" style="47" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" style="47" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" style="47" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.6640625" style="47" customWidth="1"/>
+    <col min="12" max="12" width="49" style="47" customWidth="1"/>
+    <col min="13" max="13" width="20.88671875" style="47" customWidth="1"/>
+    <col min="14" max="14" width="21.5546875" style="47" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.33203125" style="47" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="21.5546875" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="29" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="29" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="C1" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="D1" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="E1" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="F1" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="G1" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="H1" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="I1" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="J1" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="J1" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="K1" s="26" t="s">
+      <c r="L1" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="26" t="s">
+      <c r="M1" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="26" t="s">
+      <c r="N1" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="O1" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="O1" s="28" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" s="41" customFormat="1" ht="67.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:15" s="41" customFormat="1" ht="66" x14ac:dyDescent="0.25">
       <c r="A2" s="30">
         <v>1</v>
       </c>
       <c r="B2" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="D2" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="E2" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="F2" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="G2" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="H2" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="36" t="s">
-        <v>71</v>
-      </c>
       <c r="I2" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J2" s="38">
         <f>IF(H2="NA","NA",IF(H2="Yes",10,0))</f>
         <v>10</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L2" s="39" t="s">
-        <v>74</v>
+        <v>301</v>
       </c>
       <c r="M2" s="33"/>
       <c r="N2" s="33"/>
       <c r="O2" s="40"/>
     </row>
-    <row r="3" spans="1:15" s="41" customFormat="1" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" s="41" customFormat="1" ht="66" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
         <v>2</v>
       </c>
       <c r="B3" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="D3" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="E3" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="E3" s="33" t="s">
-        <v>68</v>
-      </c>
       <c r="F3" s="34" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G3" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="36" t="s">
-        <v>71</v>
-      </c>
       <c r="I3" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J3" s="38">
         <f t="shared" ref="J3:J5" si="0">IF(H3="NA","NA",IF(H3="Yes",10,0))</f>
         <v>10</v>
       </c>
       <c r="K3" s="33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L3" s="39" t="s">
-        <v>76</v>
+        <v>302</v>
       </c>
       <c r="M3" s="33"/>
       <c r="N3" s="33"/>
       <c r="O3" s="40"/>
     </row>
-    <row r="4" spans="1:15" s="41" customFormat="1" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" s="41" customFormat="1" ht="66" x14ac:dyDescent="0.25">
       <c r="A4" s="30">
         <v>3</v>
       </c>
       <c r="B4" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="D4" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="E4" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="33" t="s">
-        <v>68</v>
-      </c>
       <c r="F4" s="34" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G4" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="36" t="s">
-        <v>71</v>
-      </c>
       <c r="I4" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J4" s="38">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L4" s="39" t="s">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="M4" s="33"/>
       <c r="N4" s="33"/>
       <c r="O4" s="40"/>
     </row>
-    <row r="5" spans="1:15" s="41" customFormat="1" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" s="41" customFormat="1" ht="66" x14ac:dyDescent="0.25">
       <c r="A5" s="30">
         <v>4</v>
       </c>
       <c r="B5" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="D5" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="E5" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="33" t="s">
-        <v>68</v>
-      </c>
       <c r="F5" s="34" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G5" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="H5" s="36" t="s">
-        <v>71</v>
-      </c>
       <c r="I5" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J5" s="38">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L5" s="39" t="s">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="M5" s="33"/>
       <c r="N5" s="33"/>
       <c r="O5" s="40"/>
     </row>
-    <row r="6" spans="1:15" s="41" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" s="41" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>5</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H6" s="36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I6" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J6" s="38">
         <f t="shared" ref="J6:J15" si="1">IF(H6="NA","NA",IF(H6="Yes",10,IF(I6=1,8,IF(I6=2,6,IF(I6=3,4,IF(I6=4,2,IF(I6&gt;=4,0)))))))</f>
@@ -3248,39 +3032,39 @@
       </c>
       <c r="K6" s="33"/>
       <c r="L6" s="42" t="s">
-        <v>86</v>
+        <v>309</v>
       </c>
       <c r="M6" s="33"/>
       <c r="N6" s="33"/>
       <c r="O6" s="40"/>
     </row>
-    <row r="7" spans="1:15" s="41" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" s="41" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A7" s="30">
         <v>6</v>
       </c>
       <c r="B7" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>87</v>
-      </c>
       <c r="G7" s="35" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J7" s="38">
         <f t="shared" si="1"/>
@@ -3288,39 +3072,39 @@
       </c>
       <c r="K7" s="33"/>
       <c r="L7" s="42" t="s">
-        <v>86</v>
+        <v>309</v>
       </c>
       <c r="M7" s="33"/>
       <c r="N7" s="33"/>
       <c r="O7" s="40"/>
     </row>
-    <row r="8" spans="1:15" s="41" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" s="41" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A8" s="30">
         <v>7</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C8" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>88</v>
-      </c>
       <c r="G8" s="35" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H8" s="36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I8" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J8" s="38">
         <f t="shared" si="1"/>
@@ -3328,39 +3112,39 @@
       </c>
       <c r="K8" s="33"/>
       <c r="L8" s="42" t="s">
-        <v>86</v>
+        <v>309</v>
       </c>
       <c r="M8" s="33"/>
       <c r="N8" s="33"/>
       <c r="O8" s="40"/>
     </row>
-    <row r="9" spans="1:15" s="41" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" s="41" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A9" s="30">
         <v>8</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="F9" s="34" t="s">
-        <v>89</v>
-      </c>
       <c r="G9" s="35" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H9" s="36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I9" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J9" s="38">
         <f t="shared" si="1"/>
@@ -3368,39 +3152,39 @@
       </c>
       <c r="K9" s="33"/>
       <c r="L9" s="42" t="s">
-        <v>86</v>
+        <v>309</v>
       </c>
       <c r="M9" s="33"/>
       <c r="N9" s="33"/>
       <c r="O9" s="40"/>
     </row>
-    <row r="10" spans="1:15" s="41" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" s="41" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A10" s="30">
         <v>9</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H10" s="36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J10" s="38">
         <f t="shared" si="1"/>
@@ -3408,39 +3192,39 @@
       </c>
       <c r="K10" s="33"/>
       <c r="L10" s="42" t="s">
-        <v>86</v>
+        <v>309</v>
       </c>
       <c r="M10" s="33"/>
       <c r="N10" s="33"/>
       <c r="O10" s="40"/>
     </row>
-    <row r="11" spans="1:15" s="41" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" s="41" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A11" s="30">
         <v>10</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H11" s="36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I11" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J11" s="38">
         <f t="shared" si="1"/>
@@ -3448,39 +3232,39 @@
       </c>
       <c r="K11" s="33"/>
       <c r="L11" s="42" t="s">
-        <v>86</v>
+        <v>309</v>
       </c>
       <c r="M11" s="33"/>
       <c r="N11" s="33"/>
       <c r="O11" s="40"/>
     </row>
-    <row r="12" spans="1:15" s="41" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" s="41" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A12" s="30">
         <v>11</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J12" s="38" t="str">
         <f t="shared" si="1"/>
@@ -3488,39 +3272,39 @@
       </c>
       <c r="K12" s="33"/>
       <c r="L12" s="42" t="s">
-        <v>93</v>
+        <v>283</v>
       </c>
       <c r="M12" s="33"/>
       <c r="N12" s="33"/>
       <c r="O12" s="40"/>
     </row>
-    <row r="13" spans="1:15" s="41" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" s="41" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A13" s="30">
         <v>12</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H13" s="36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I13" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J13" s="38">
         <f t="shared" si="1"/>
@@ -3528,39 +3312,39 @@
       </c>
       <c r="K13" s="33"/>
       <c r="L13" s="42" t="s">
-        <v>86</v>
+        <v>309</v>
       </c>
       <c r="M13" s="33"/>
       <c r="N13" s="33"/>
       <c r="O13" s="40"/>
     </row>
-    <row r="14" spans="1:15" s="41" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" s="41" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A14" s="30">
         <v>13</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H14" s="36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J14" s="38">
         <f t="shared" si="1"/>
@@ -3568,39 +3352,39 @@
       </c>
       <c r="K14" s="33"/>
       <c r="L14" s="42" t="s">
-        <v>86</v>
+        <v>309</v>
       </c>
       <c r="M14" s="33"/>
       <c r="N14" s="33"/>
       <c r="O14" s="40"/>
     </row>
-    <row r="15" spans="1:15" s="41" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" s="41" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>14</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J15" s="38" t="str">
         <f t="shared" si="1"/>
@@ -3608,39 +3392,39 @@
       </c>
       <c r="K15" s="33"/>
       <c r="L15" s="42" t="s">
-        <v>97</v>
+        <v>304</v>
       </c>
       <c r="M15" s="33"/>
       <c r="N15" s="33"/>
       <c r="O15" s="40"/>
     </row>
-    <row r="16" spans="1:15" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="66" x14ac:dyDescent="0.3">
       <c r="A16" s="30">
         <v>15</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E16" s="42" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G16" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="H16" s="36" t="s">
-        <v>71</v>
-      </c>
       <c r="I16" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J16" s="38">
         <f>IF(H16="NA","NA",IF(H16="Yes",10,0))</f>
@@ -3648,483 +3432,483 @@
       </c>
       <c r="K16" s="45"/>
       <c r="L16" s="42" t="s">
-        <v>86</v>
+        <v>309</v>
       </c>
       <c r="M16" s="42"/>
       <c r="N16" s="42"/>
       <c r="O16" s="40"/>
     </row>
-    <row r="17" spans="1:15" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A17" s="30">
         <v>16</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E17" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="F17" s="47" t="s">
-        <v>105</v>
+        <v>96</v>
+      </c>
+      <c r="F17" s="48" t="s">
+        <v>97</v>
       </c>
       <c r="G17" s="42" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H17" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I17" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="J17" s="48" t="str">
+        <v>71</v>
+      </c>
+      <c r="J17" s="49" t="str">
         <f>IF(H17="NA","NA",IF(H17="Yes",10,IF(I17=1,5,0)))</f>
         <v>NA</v>
       </c>
-      <c r="K17" s="49"/>
+      <c r="K17" s="50"/>
       <c r="L17" s="42" t="s">
-        <v>93</v>
+        <v>283</v>
       </c>
       <c r="M17" s="42"/>
       <c r="N17" s="42"/>
       <c r="O17" s="40"/>
     </row>
-    <row r="18" spans="1:15" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" ht="66" x14ac:dyDescent="0.25">
       <c r="A18" s="30">
         <v>17</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E18" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="F18" s="47" t="s">
-        <v>107</v>
+        <v>96</v>
+      </c>
+      <c r="F18" s="48" t="s">
+        <v>99</v>
       </c>
       <c r="G18" s="42" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H18" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I18" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="J18" s="48" t="str">
+        <v>71</v>
+      </c>
+      <c r="J18" s="49" t="str">
         <f t="shared" ref="J18" si="2">IF(H18="NA","NA",IF(H18="Yes",10,IF(I18=1,5,0)))</f>
         <v>NA</v>
       </c>
-      <c r="K18" s="49"/>
+      <c r="K18" s="50"/>
       <c r="L18" s="42" t="s">
-        <v>93</v>
+        <v>283</v>
       </c>
       <c r="M18" s="42"/>
       <c r="N18" s="42"/>
       <c r="O18" s="40"/>
     </row>
-    <row r="19" spans="1:15" ht="121.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" ht="105.6" x14ac:dyDescent="0.25">
       <c r="A19" s="30">
         <v>18</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="G19" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="50" t="s">
-        <v>109</v>
-      </c>
-      <c r="F19" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="G19" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="H19" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="I19" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="J19" s="52" t="str">
+      <c r="H19" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="J19" s="53" t="str">
         <f>IF(H19="NA","NA",IF(H19="Yes",10,IF(H19="Critical",-10,IF(I19=1,-2,IF(I19=2,-4,IF(I19=3,-6,IF(I19=4,-8,-10)))))))</f>
         <v>NA</v>
       </c>
-      <c r="K19" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="L19" s="54" t="s">
-        <v>113</v>
+      <c r="K19" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="L19" s="46" t="s">
+        <v>281</v>
       </c>
       <c r="M19" s="42"/>
       <c r="N19" s="42"/>
       <c r="O19" s="40"/>
     </row>
-    <row r="20" spans="1:15" ht="256.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" ht="250.8" x14ac:dyDescent="0.25">
       <c r="A20" s="30">
         <v>19</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C20" s="55" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D20" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="F20" s="50" t="s">
-        <v>116</v>
+        <v>66</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>274</v>
       </c>
       <c r="G20" s="35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H20" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J20" s="38" t="str">
         <f t="shared" ref="J20:J25" si="3">IF(H20="NA","NA",IF(H20="Yes",10,0))</f>
         <v>NA</v>
       </c>
       <c r="K20" s="56"/>
-      <c r="L20" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="M20" s="50"/>
-      <c r="N20" s="50"/>
+      <c r="L20" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="M20" s="51"/>
+      <c r="N20" s="51"/>
       <c r="O20" s="57"/>
     </row>
-    <row r="21" spans="1:15" ht="256.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" ht="250.8" x14ac:dyDescent="0.25">
       <c r="A21" s="30">
         <v>20</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C21" s="55" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D21" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="F21" s="50" t="s">
-        <v>117</v>
+        <v>66</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>275</v>
       </c>
       <c r="G21" s="35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H21" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J21" s="38" t="str">
         <f t="shared" si="3"/>
         <v>NA</v>
       </c>
       <c r="K21" s="56"/>
-      <c r="L21" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="M21" s="50"/>
-      <c r="N21" s="50"/>
+      <c r="L21" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="M21" s="51"/>
+      <c r="N21" s="51"/>
       <c r="O21" s="57"/>
     </row>
-    <row r="22" spans="1:15" ht="256.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" ht="250.8" x14ac:dyDescent="0.25">
       <c r="A22" s="30">
         <v>21</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D22" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="F22" s="50" t="s">
-        <v>118</v>
+        <v>66</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="51" t="s">
+        <v>276</v>
       </c>
       <c r="G22" s="35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H22" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J22" s="38" t="str">
         <f t="shared" si="3"/>
         <v>NA</v>
       </c>
       <c r="K22" s="56"/>
-      <c r="L22" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="M22" s="50"/>
-      <c r="N22" s="50"/>
+      <c r="L22" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="M22" s="51"/>
+      <c r="N22" s="51"/>
       <c r="O22" s="57"/>
     </row>
-    <row r="23" spans="1:15" ht="256.5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" ht="250.8" x14ac:dyDescent="0.25">
       <c r="A23" s="30">
         <v>22</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C23" s="55" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D23" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="F23" s="50" t="s">
-        <v>119</v>
+        <v>66</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>277</v>
       </c>
       <c r="G23" s="35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H23" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J23" s="38" t="str">
         <f t="shared" si="3"/>
         <v>NA</v>
       </c>
       <c r="K23" s="56"/>
-      <c r="L23" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="M23" s="50"/>
-      <c r="N23" s="50"/>
+      <c r="L23" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="M23" s="51"/>
+      <c r="N23" s="51"/>
       <c r="O23" s="57"/>
     </row>
-    <row r="24" spans="1:15" ht="256.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" ht="250.8" x14ac:dyDescent="0.25">
       <c r="A24" s="30">
         <v>23</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D24" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E24" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="F24" s="50" t="s">
-        <v>120</v>
+        <v>66</v>
+      </c>
+      <c r="E24" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="F24" s="51" t="s">
+        <v>278</v>
       </c>
       <c r="G24" s="35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J24" s="38" t="str">
         <f t="shared" si="3"/>
         <v>NA</v>
       </c>
       <c r="K24" s="56"/>
-      <c r="L24" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="M24" s="50"/>
-      <c r="N24" s="50"/>
+      <c r="L24" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="M24" s="51"/>
+      <c r="N24" s="51"/>
       <c r="O24" s="57"/>
     </row>
-    <row r="25" spans="1:15" ht="256.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" ht="250.8" x14ac:dyDescent="0.25">
       <c r="A25" s="30">
         <v>24</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="F25" s="50" t="s">
-        <v>121</v>
+        <v>66</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>279</v>
       </c>
       <c r="G25" s="35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H25" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J25" s="38" t="str">
         <f t="shared" si="3"/>
         <v>NA</v>
       </c>
       <c r="K25" s="56"/>
-      <c r="L25" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="M25" s="50"/>
-      <c r="N25" s="50"/>
+      <c r="L25" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="M25" s="51"/>
+      <c r="N25" s="51"/>
       <c r="O25" s="57"/>
     </row>
-    <row r="26" spans="1:15" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A26" s="30">
         <v>25</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D26" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="F26" s="50" t="s">
-        <v>125</v>
-      </c>
-      <c r="G26" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="H26" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="I26" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="J26" s="52">
+        <v>66</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="H26" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="I26" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="J26" s="53">
         <f>IF(H26="NA","NA",IF(H26="Yes",10,IF(I26=1,-2,IF(I26=2,-4,IF(I26=3,-6,IF(I26=4,-8,-10))))))</f>
         <v>10</v>
       </c>
       <c r="K26" s="56"/>
       <c r="L26" s="58" t="s">
-        <v>127</v>
+        <v>284</v>
       </c>
       <c r="M26" s="58"/>
       <c r="N26" s="58"/>
       <c r="O26" s="57"/>
     </row>
-    <row r="27" spans="1:15" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A27" s="30">
         <v>26</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="C27" s="55" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="F27" s="50" t="s">
-        <v>131</v>
-      </c>
-      <c r="G27" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="H27" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="I27" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="J27" s="52">
+        <v>66</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="G27" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="H27" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="I27" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="J27" s="53">
         <f>IF(H27="NA","NA",IF(H27="Yes",10,IF(I27=1,-2,IF(I27=2,-4,IF(I27=3,-6,IF(I27=4,-8,-10))))))</f>
         <v>10</v>
       </c>
-      <c r="K27" s="53" t="s">
+      <c r="K27" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="L27" s="50" t="s">
-        <v>132</v>
-      </c>
-      <c r="M27" s="50"/>
-      <c r="N27" s="50"/>
+      <c r="L27" s="51" t="s">
+        <v>285</v>
+      </c>
+      <c r="M27" s="51"/>
+      <c r="N27" s="51"/>
       <c r="O27" s="57"/>
     </row>
-    <row r="28" spans="1:15" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A28" s="30">
         <v>27</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C28" s="55" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D28" s="55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E28" s="42" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="F28" s="42" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="G28" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="H28" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="I28" s="51" t="s">
-        <v>72</v>
+        <v>80</v>
+      </c>
+      <c r="H28" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="I28" s="52" t="s">
+        <v>71</v>
       </c>
       <c r="J28" s="59" t="str">
         <f>IF(H28="NA","NA",IF(H28="Yes",10,IF(I28=1,8,IF(I28=2,6,IF(I28=3,4,IF(I28=4,2,0))))))</f>
@@ -4134,21 +3918,21 @@
         <v>6</v>
       </c>
       <c r="L28" s="60" t="s">
-        <v>134</v>
+        <v>286</v>
       </c>
       <c r="M28" s="60"/>
       <c r="N28" s="60"/>
       <c r="O28" s="57"/>
     </row>
-    <row r="29" spans="1:15" s="70" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="62"/>
       <c r="C29" s="63"/>
       <c r="D29" s="63"/>
       <c r="E29" s="64" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F29" s="64"/>
       <c r="G29" s="64"/>
@@ -4164,277 +3948,277 @@
       <c r="N29" s="68"/>
       <c r="O29" s="69"/>
     </row>
-    <row r="30" spans="1:15" s="70" customFormat="1" ht="81" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" s="70" customFormat="1" ht="66" x14ac:dyDescent="0.25">
       <c r="A30" s="71">
         <v>28</v>
       </c>
       <c r="B30" s="72" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C30" s="55" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D30" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" s="50" t="s">
-        <v>138</v>
+        <v>95</v>
+      </c>
+      <c r="E30" s="51" t="s">
+        <v>120</v>
       </c>
       <c r="F30" s="73" t="s">
-        <v>139</v>
-      </c>
-      <c r="G30" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="H30" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="I30" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="J30" s="52">
+        <v>121</v>
+      </c>
+      <c r="G30" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="H30" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="I30" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="J30" s="53">
         <f>IF(H30="NA","NA",IF(H30="Yes",10,IF(I30=1,-2,IF(I30=2,-4,IF(I30=3,-6,IF(I30=4,-8,-10))))))</f>
         <v>10</v>
       </c>
-      <c r="K30" s="50"/>
-      <c r="L30" s="50" t="s">
-        <v>140</v>
-      </c>
-      <c r="M30" s="50"/>
-      <c r="N30" s="50"/>
+      <c r="K30" s="51"/>
+      <c r="L30" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="M30" s="51"/>
+      <c r="N30" s="51"/>
       <c r="O30" s="57"/>
     </row>
-    <row r="31" spans="1:15" s="70" customFormat="1" ht="81" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" s="70" customFormat="1" ht="66" x14ac:dyDescent="0.25">
       <c r="A31" s="71">
         <v>29</v>
       </c>
       <c r="B31" s="72" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C31" s="55" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D31" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E31" s="50" t="s">
-        <v>138</v>
+        <v>95</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>120</v>
       </c>
       <c r="F31" s="73" t="s">
-        <v>141</v>
-      </c>
-      <c r="G31" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="H31" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="I31" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="J31" s="52">
+        <v>122</v>
+      </c>
+      <c r="G31" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="H31" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="I31" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="J31" s="53">
         <f>IF(H31="NA","NA",IF(H31="Yes",10,IF(I31=1,-2,IF(I31=2,-4,IF(I31=3,-6,IF(I31=4,-8,-10))))))</f>
         <v>10</v>
       </c>
-      <c r="K31" s="50"/>
-      <c r="L31" s="50" t="s">
-        <v>140</v>
-      </c>
-      <c r="M31" s="50"/>
-      <c r="N31" s="50"/>
+      <c r="K31" s="51"/>
+      <c r="L31" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="M31" s="51"/>
+      <c r="N31" s="51"/>
       <c r="O31" s="57"/>
     </row>
-    <row r="32" spans="1:15" s="70" customFormat="1" ht="108" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" s="70" customFormat="1" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A32" s="71">
         <v>30</v>
       </c>
       <c r="B32" s="72" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C32" s="32" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="D32" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E32" s="50" t="s">
-        <v>143</v>
+        <v>66</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>124</v>
       </c>
       <c r="F32" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="G32" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="H32" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="I32" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="J32" s="52">
+        <v>125</v>
+      </c>
+      <c r="G32" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="H32" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="I32" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="J32" s="53">
         <f>IF(H32="NA","NA",IF(H32="Yes",10,IF(I32=1,-2,IF(I32=2,-4,IF(I32=3,-6,IF(I32=4,-8,-10))))))</f>
         <v>10</v>
       </c>
       <c r="K32" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="L32" s="50" t="s">
-        <v>140</v>
-      </c>
-      <c r="M32" s="50"/>
-      <c r="N32" s="50"/>
+        <v>126</v>
+      </c>
+      <c r="L32" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="M32" s="51"/>
+      <c r="N32" s="51"/>
       <c r="O32" s="57"/>
     </row>
-    <row r="33" spans="1:15" s="74" customFormat="1" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" s="74" customFormat="1" ht="66" x14ac:dyDescent="0.25">
       <c r="A33" s="71">
         <v>31</v>
       </c>
       <c r="B33" s="72" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D33" s="55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="F33" s="49" t="s">
-        <v>148</v>
+        <v>128</v>
+      </c>
+      <c r="F33" s="50" t="s">
+        <v>129</v>
       </c>
       <c r="G33" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="H33" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="I33" s="51" t="s">
-        <v>72</v>
+        <v>80</v>
+      </c>
+      <c r="H33" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="I33" s="52" t="s">
+        <v>71</v>
       </c>
       <c r="J33" s="59" t="str">
-        <f t="shared" ref="J33:J35" si="4">IF(H33="NA","NA",IF(H33="Yes",10,IF(I33=1,8,IF(I33=2,6,IF(I33=3,4,IF(I33=4,2,0))))))</f>
+        <f t="shared" ref="J33" si="4">IF(H33="NA","NA",IF(H33="Yes",10,IF(I33=1,8,IF(I33=2,6,IF(I33=3,4,IF(I33=4,2,0))))))</f>
         <v>NA</v>
       </c>
       <c r="K33" s="33"/>
-      <c r="L33" s="50" t="s">
-        <v>113</v>
+      <c r="L33" s="51" t="s">
+        <v>281</v>
       </c>
       <c r="M33" s="42"/>
       <c r="N33" s="42"/>
       <c r="O33" s="40"/>
     </row>
-    <row r="34" spans="1:15" s="74" customFormat="1" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" s="74" customFormat="1" ht="66" x14ac:dyDescent="0.25">
       <c r="A34" s="71">
         <v>32</v>
       </c>
       <c r="B34" s="72" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C34" s="55" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D34" s="55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F34" s="42" t="s">
-        <v>149</v>
+        <v>273</v>
       </c>
       <c r="G34" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="H34" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="I34" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="J34" s="59">
-        <f t="shared" si="4"/>
-        <v>10</v>
+        <v>80</v>
+      </c>
+      <c r="H34" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="I34" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="J34" s="59" t="str">
+        <f t="shared" ref="J34:J35" si="5">IF(H34="NA","NA",IF(H34="Yes",10,IF(I34=1,8,IF(I34=2,6,IF(I34=3,4,IF(I34=4,2,0))))))</f>
+        <v>NA</v>
       </c>
       <c r="K34" s="33"/>
-      <c r="L34" s="50" t="s">
-        <v>323</v>
+      <c r="L34" s="51" t="s">
+        <v>281</v>
       </c>
       <c r="M34" s="42"/>
       <c r="N34" s="42"/>
       <c r="O34" s="40"/>
     </row>
-    <row r="35" spans="1:15" s="74" customFormat="1" ht="81" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" s="74" customFormat="1" ht="66" x14ac:dyDescent="0.25">
       <c r="A35" s="71">
         <v>33</v>
       </c>
       <c r="B35" s="72" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C35" s="32" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="D35" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E35" s="49" t="s">
-        <v>151</v>
+        <v>66</v>
+      </c>
+      <c r="E35" s="50" t="s">
+        <v>131</v>
       </c>
       <c r="F35" s="42" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="G35" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="H35" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="I35" s="51" t="s">
-        <v>72</v>
+        <v>80</v>
+      </c>
+      <c r="H35" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="I35" s="52" t="s">
+        <v>71</v>
       </c>
       <c r="J35" s="59">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="K35" s="42" t="s">
-        <v>153</v>
-      </c>
-      <c r="L35" s="50" t="s">
-        <v>154</v>
+        <v>133</v>
+      </c>
+      <c r="L35" s="51" t="s">
+        <v>303</v>
       </c>
       <c r="M35" s="33"/>
       <c r="N35" s="33"/>
       <c r="O35" s="40"/>
     </row>
-    <row r="36" spans="1:15" s="74" customFormat="1" ht="54" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" s="74" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A36" s="71">
         <v>34</v>
       </c>
       <c r="B36" s="72" t="s">
+        <v>118</v>
+      </c>
+      <c r="C36" s="55" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="E36" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="F36" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="C36" s="55" t="s">
-        <v>155</v>
-      </c>
-      <c r="D36" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E36" s="42" t="s">
-        <v>156</v>
-      </c>
-      <c r="F36" s="49" t="s">
-        <v>157</v>
-      </c>
       <c r="G36" s="35" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J36" s="37">
         <f>IF(H36="NA","NA",IF(H36="Yes",10,IF(H36="critical",-10,0)))</f>
@@ -4442,433 +4226,433 @@
       </c>
       <c r="K36" s="42"/>
       <c r="L36" s="42" t="s">
-        <v>140</v>
+        <v>282</v>
       </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
       <c r="O36" s="40"/>
     </row>
-    <row r="37" spans="1:15" s="74" customFormat="1" ht="202.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" s="74" customFormat="1" ht="184.8" x14ac:dyDescent="0.25">
       <c r="A37" s="71">
         <v>35</v>
       </c>
       <c r="B37" s="72" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="C37" s="55" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="D37" s="55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E37" s="42" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="F37" s="42" t="s">
-        <v>162</v>
-      </c>
-      <c r="G37" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="H37" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="I37" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="J37" s="52">
+        <v>141</v>
+      </c>
+      <c r="G37" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="H37" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="I37" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="J37" s="53">
         <f>IF(H37="NA","NA",IF(H37="Yes",10,IF(I37=1,-2,IF(I37=2,-4,IF(I37=3,-6,IF(I37=4,-8,-10))))))</f>
         <v>10</v>
       </c>
       <c r="K37" s="45" t="s">
-        <v>163</v>
-      </c>
-      <c r="L37" s="50" t="s">
-        <v>164</v>
+        <v>142</v>
+      </c>
+      <c r="L37" s="51" t="s">
+        <v>310</v>
       </c>
       <c r="M37" s="33"/>
       <c r="N37" s="33"/>
       <c r="O37" s="40"/>
     </row>
-    <row r="38" spans="1:15" s="74" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" s="74" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A38" s="71">
         <v>36</v>
       </c>
       <c r="B38" s="72" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="C38" s="55" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="D38" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E38" s="49" t="s">
-        <v>166</v>
-      </c>
-      <c r="F38" s="47" t="s">
-        <v>167</v>
+        <v>95</v>
+      </c>
+      <c r="E38" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38" s="48" t="s">
+        <v>145</v>
       </c>
       <c r="G38" s="35" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J38" s="37">
         <f>IF(H38="NA","NA",IF(H38="Critical",-10,IF(H38="Yes",10,IF(I38=1,-2,IF(I38=2,-4,IF(I38=3,-6,IF(I38=4,-8,-10)))))))</f>
         <v>10</v>
       </c>
-      <c r="K38" s="50"/>
+      <c r="K38" s="51"/>
       <c r="L38" s="33" t="s">
-        <v>169</v>
+        <v>305</v>
       </c>
       <c r="M38" s="33"/>
       <c r="N38" s="33"/>
       <c r="O38" s="40"/>
     </row>
-    <row r="39" spans="1:15" s="74" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" s="74" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A39" s="71">
         <v>37</v>
       </c>
       <c r="B39" s="72" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="C39" s="55" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="D39" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E39" s="49" t="s">
-        <v>166</v>
-      </c>
-      <c r="F39" s="47" t="s">
-        <v>170</v>
+        <v>95</v>
+      </c>
+      <c r="E39" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="F39" s="48" t="s">
+        <v>147</v>
       </c>
       <c r="G39" s="35" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I39" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J39" s="37">
-        <f t="shared" ref="J39:J41" si="5">IF(H39="NA","NA",IF(H39="Critical",-10,IF(H39="Yes",10,IF(I39=1,-2,IF(I39=2,-4,IF(I39=3,-6,IF(I39=4,-8,-10)))))))</f>
+        <f t="shared" ref="J39:J41" si="6">IF(H39="NA","NA",IF(H39="Critical",-10,IF(H39="Yes",10,IF(I39=1,-2,IF(I39=2,-4,IF(I39=3,-6,IF(I39=4,-8,-10)))))))</f>
         <v>10</v>
       </c>
-      <c r="K39" s="50"/>
+      <c r="K39" s="51"/>
       <c r="L39" s="33" t="s">
-        <v>171</v>
+        <v>306</v>
       </c>
       <c r="M39" s="33"/>
       <c r="N39" s="33"/>
       <c r="O39" s="40"/>
     </row>
-    <row r="40" spans="1:15" s="74" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" s="74" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A40" s="71">
         <v>38</v>
       </c>
       <c r="B40" s="72" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="C40" s="55" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="D40" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E40" s="49" t="s">
-        <v>166</v>
+        <v>95</v>
+      </c>
+      <c r="E40" s="50" t="s">
+        <v>144</v>
       </c>
       <c r="F40" s="75" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="G40" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="H40" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="I40" s="51" t="s">
-        <v>72</v>
+        <v>146</v>
+      </c>
+      <c r="H40" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="I40" s="52" t="s">
+        <v>71</v>
       </c>
       <c r="J40" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="K40" s="50"/>
+      <c r="K40" s="51"/>
       <c r="L40" s="33" t="s">
-        <v>173</v>
+        <v>311</v>
       </c>
       <c r="M40" s="33"/>
       <c r="N40" s="33"/>
       <c r="O40" s="40"/>
     </row>
-    <row r="41" spans="1:15" s="74" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" s="74" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A41" s="71">
         <v>39</v>
       </c>
       <c r="B41" s="72" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="D41" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E41" s="49" t="s">
-        <v>166</v>
+        <v>95</v>
+      </c>
+      <c r="E41" s="50" t="s">
+        <v>144</v>
       </c>
       <c r="F41" s="75" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="G41" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="H41" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="I41" s="51" t="s">
-        <v>72</v>
+        <v>146</v>
+      </c>
+      <c r="H41" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="I41" s="52" t="s">
+        <v>71</v>
       </c>
       <c r="J41" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="K41" s="50"/>
+      <c r="K41" s="51"/>
       <c r="L41" s="33" t="s">
-        <v>175</v>
+        <v>312</v>
       </c>
       <c r="M41" s="33"/>
       <c r="N41" s="33"/>
       <c r="O41" s="40"/>
     </row>
-    <row r="42" spans="1:15" s="74" customFormat="1" ht="81" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" s="74" customFormat="1" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A42" s="71">
         <v>40</v>
       </c>
       <c r="B42" s="72" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="D42" s="55" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E42" s="42" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="F42" s="42" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="G42" s="42" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J42" s="37">
         <f>IF(H42="NA","NA",IF(H42="Critical",-10,IF(H42="Yes",10,IF(I42=1,-2,IF(I42=2,-4,IF(I42=3,-6,IF(I42=4,-8,-10)))))))</f>
         <v>10</v>
       </c>
       <c r="K42" s="45" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="L42" s="33" t="s">
-        <v>180</v>
+        <v>287</v>
       </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
       <c r="O42" s="40"/>
     </row>
-    <row r="43" spans="1:15" s="74" customFormat="1" ht="54" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" s="74" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A43" s="71">
         <v>41</v>
       </c>
       <c r="B43" s="72" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="C43" s="55" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="D43" s="55" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>183</v>
-      </c>
-      <c r="F43" s="47" t="s">
-        <v>184</v>
+        <v>156</v>
+      </c>
+      <c r="F43" s="48" t="s">
+        <v>157</v>
       </c>
       <c r="G43" s="35" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J43" s="37">
-        <f t="shared" ref="J43:J46" si="6">IF(H43="NA","NA",IF(H43="Critical",-10,IF(H43="Yes",10,IF(I43=1,-2,IF(I43=2,-4,IF(I43=3,-6,IF(I43=4,-8,-10)))))))</f>
+        <f t="shared" ref="J43:J46" si="7">IF(H43="NA","NA",IF(H43="Critical",-10,IF(H43="Yes",10,IF(I43=1,-2,IF(I43=2,-4,IF(I43=3,-6,IF(I43=4,-8,-10)))))))</f>
         <v>10</v>
       </c>
-      <c r="K43" s="50" t="s">
-        <v>185</v>
+      <c r="K43" s="51" t="s">
+        <v>158</v>
       </c>
       <c r="L43" s="42" t="s">
-        <v>186</v>
+        <v>288</v>
       </c>
       <c r="M43" s="42"/>
       <c r="N43" s="42"/>
       <c r="O43" s="40"/>
     </row>
-    <row r="44" spans="1:15" s="74" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" s="74" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A44" s="71">
         <v>42</v>
       </c>
       <c r="B44" s="72" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="C44" s="55" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="D44" s="55" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E44" s="42" t="s">
-        <v>183</v>
-      </c>
-      <c r="F44" s="47" t="s">
-        <v>187</v>
+        <v>156</v>
+      </c>
+      <c r="F44" s="48" t="s">
+        <v>159</v>
       </c>
       <c r="G44" s="35" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J44" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="K44" s="50" t="s">
-        <v>185</v>
+      <c r="K44" s="51" t="s">
+        <v>158</v>
       </c>
       <c r="L44" s="42" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="M44" s="42"/>
       <c r="N44" s="42"/>
       <c r="O44" s="40"/>
     </row>
-    <row r="45" spans="1:15" s="74" customFormat="1" ht="81" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" s="74" customFormat="1" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A45" s="71">
         <v>43</v>
       </c>
       <c r="B45" s="72" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="C45" s="55" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D45" s="55" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E45" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="F45" s="47" t="s">
-        <v>192</v>
+        <v>162</v>
+      </c>
+      <c r="F45" s="48" t="s">
+        <v>163</v>
       </c>
       <c r="G45" s="35" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J45" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="K45" s="45" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="L45" s="42" t="s">
-        <v>194</v>
+        <v>289</v>
       </c>
       <c r="M45" s="42"/>
       <c r="N45" s="42"/>
       <c r="O45" s="40"/>
     </row>
-    <row r="46" spans="1:15" s="74" customFormat="1" ht="81" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" s="74" customFormat="1" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A46" s="71">
         <v>44</v>
       </c>
       <c r="B46" s="72" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="C46" s="55" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D46" s="55" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E46" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="F46" s="47" t="s">
-        <v>187</v>
+        <v>162</v>
+      </c>
+      <c r="F46" s="48" t="s">
+        <v>159</v>
       </c>
       <c r="G46" s="35" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J46" s="37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="K46" s="45" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="L46" s="42" t="s">
-        <v>195</v>
+        <v>308</v>
       </c>
       <c r="M46" s="42"/>
       <c r="N46" s="42"/>
       <c r="O46" s="40"/>
     </row>
-    <row r="47" spans="1:15" s="76" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" s="76" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B47" s="62"/>
       <c r="C47" s="63"/>
       <c r="D47" s="63"/>
       <c r="E47" s="64" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F47" s="64"/>
       <c r="G47" s="64"/>
@@ -4884,433 +4668,433 @@
       <c r="N47" s="68"/>
       <c r="O47" s="69"/>
     </row>
-    <row r="48" spans="1:15" s="74" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" s="74" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A48" s="71">
         <v>45</v>
       </c>
       <c r="B48" s="72" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="C48" s="55" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="D48" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E48" s="50" t="s">
-        <v>198</v>
+        <v>66</v>
+      </c>
+      <c r="E48" s="51" t="s">
+        <v>167</v>
       </c>
       <c r="F48" s="77" t="s">
-        <v>199</v>
-      </c>
-      <c r="G48" s="50" t="s">
-        <v>200</v>
+        <v>168</v>
+      </c>
+      <c r="G48" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="H48" s="78" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I48" s="79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J48" s="78">
         <f>IF(H48="NA","NA",IF(H48="Yes",10,IF(I48=1,-5,IF(I48=2,-10,IF(I48=3,-15,-20)))))</f>
         <v>10</v>
       </c>
-      <c r="K48" s="50" t="s">
-        <v>201</v>
-      </c>
-      <c r="L48" s="50" t="s">
-        <v>202</v>
+      <c r="K48" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="L48" s="51" t="s">
+        <v>290</v>
       </c>
       <c r="M48" s="33"/>
       <c r="N48" s="33"/>
       <c r="O48" s="40"/>
     </row>
-    <row r="49" spans="1:15" s="74" customFormat="1" ht="166.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" s="74" customFormat="1" ht="139.19999999999999" x14ac:dyDescent="0.25">
       <c r="A49" s="71">
         <v>46</v>
       </c>
       <c r="B49" s="72" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="C49" s="32" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="D49" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="E49" s="50" t="s">
-        <v>203</v>
+        <v>66</v>
+      </c>
+      <c r="E49" s="51" t="s">
+        <v>171</v>
       </c>
       <c r="F49" s="45" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="G49" s="42" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="H49" s="80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I49" s="80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J49" s="80">
-        <f t="shared" ref="J49" si="7">IF(H49="NA","NA",IF(H49="Yes",10,-10))</f>
+        <f t="shared" ref="J49" si="8">IF(H49="NA","NA",IF(H49="Yes",10,-10))</f>
         <v>10</v>
       </c>
       <c r="K49" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="L49" s="50" t="s">
-        <v>140</v>
+      <c r="L49" s="51" t="s">
+        <v>282</v>
       </c>
       <c r="M49" s="33"/>
       <c r="N49" s="33"/>
       <c r="O49" s="40"/>
     </row>
-    <row r="50" spans="1:15" s="74" customFormat="1" ht="54" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" s="74" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A50" s="71">
         <v>47</v>
       </c>
       <c r="B50" s="72" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="C50" s="55" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="D50" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E50" s="50" t="s">
-        <v>206</v>
+        <v>66</v>
+      </c>
+      <c r="E50" s="51" t="s">
+        <v>174</v>
       </c>
       <c r="F50" s="73" t="s">
-        <v>207</v>
-      </c>
-      <c r="G50" s="50" t="s">
-        <v>200</v>
+        <v>175</v>
+      </c>
+      <c r="G50" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="H50" s="78" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I50" s="79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J50" s="78">
-        <f t="shared" ref="J50:J55" si="8">IF(H50="NA","NA",IF(H50="Yes",10,IF(I50=1,-5,IF(I50=2,-10,IF(I50=3,-15,-20)))))</f>
+        <f t="shared" ref="J50:J55" si="9">IF(H50="NA","NA",IF(H50="Yes",10,IF(I50=1,-5,IF(I50=2,-10,IF(I50=3,-15,-20)))))</f>
         <v>10</v>
       </c>
       <c r="K50" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="L50" s="50" t="s">
-        <v>140</v>
+      <c r="L50" s="51" t="s">
+        <v>282</v>
       </c>
       <c r="M50" s="33"/>
       <c r="N50" s="33"/>
       <c r="O50" s="40"/>
     </row>
-    <row r="51" spans="1:15" s="74" customFormat="1" ht="54" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" s="74" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A51" s="71">
         <v>48</v>
       </c>
       <c r="B51" s="72" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="C51" s="55" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="D51" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E51" s="50" t="s">
-        <v>206</v>
+        <v>66</v>
+      </c>
+      <c r="E51" s="51" t="s">
+        <v>174</v>
       </c>
       <c r="F51" s="73" t="s">
-        <v>208</v>
-      </c>
-      <c r="G51" s="50" t="s">
-        <v>200</v>
+        <v>176</v>
+      </c>
+      <c r="G51" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="H51" s="78" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I51" s="79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J51" s="78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="K51" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="L51" s="50" t="s">
-        <v>140</v>
+      <c r="L51" s="51" t="s">
+        <v>282</v>
       </c>
       <c r="M51" s="33"/>
       <c r="N51" s="33"/>
       <c r="O51" s="40"/>
     </row>
-    <row r="52" spans="1:15" s="74" customFormat="1" ht="54" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" s="74" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A52" s="71">
         <v>49</v>
       </c>
       <c r="B52" s="72" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="C52" s="55" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="D52" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E52" s="50" t="s">
-        <v>206</v>
+        <v>66</v>
+      </c>
+      <c r="E52" s="51" t="s">
+        <v>174</v>
       </c>
       <c r="F52" s="73" t="s">
-        <v>209</v>
-      </c>
-      <c r="G52" s="50" t="s">
-        <v>200</v>
+        <v>177</v>
+      </c>
+      <c r="G52" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="H52" s="78" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I52" s="79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J52" s="78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="K52" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="L52" s="50" t="s">
-        <v>140</v>
+      <c r="L52" s="51" t="s">
+        <v>282</v>
       </c>
       <c r="M52" s="33"/>
       <c r="N52" s="33"/>
       <c r="O52" s="40"/>
     </row>
-    <row r="53" spans="1:15" s="74" customFormat="1" ht="54" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" s="74" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A53" s="71">
         <v>50</v>
       </c>
       <c r="B53" s="72" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="C53" s="55" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="D53" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E53" s="50" t="s">
-        <v>206</v>
+        <v>66</v>
+      </c>
+      <c r="E53" s="51" t="s">
+        <v>174</v>
       </c>
       <c r="F53" s="73" t="s">
-        <v>210</v>
-      </c>
-      <c r="G53" s="50" t="s">
-        <v>200</v>
+        <v>178</v>
+      </c>
+      <c r="G53" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="H53" s="78" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I53" s="79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J53" s="78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="K53" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="L53" s="50" t="s">
-        <v>140</v>
+      <c r="L53" s="51" t="s">
+        <v>282</v>
       </c>
       <c r="M53" s="33"/>
       <c r="N53" s="33"/>
       <c r="O53" s="40"/>
     </row>
-    <row r="54" spans="1:15" s="74" customFormat="1" ht="54" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" s="74" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A54" s="71">
         <v>51</v>
       </c>
       <c r="B54" s="72" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="C54" s="55" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="D54" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E54" s="50" t="s">
-        <v>206</v>
+        <v>66</v>
+      </c>
+      <c r="E54" s="51" t="s">
+        <v>174</v>
       </c>
       <c r="F54" s="73" t="s">
-        <v>211</v>
-      </c>
-      <c r="G54" s="50" t="s">
-        <v>200</v>
+        <v>179</v>
+      </c>
+      <c r="G54" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="H54" s="78" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I54" s="79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J54" s="78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="K54" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="L54" s="50" t="s">
-        <v>140</v>
+      <c r="L54" s="51" t="s">
+        <v>282</v>
       </c>
       <c r="M54" s="33"/>
       <c r="N54" s="33"/>
       <c r="O54" s="40"/>
     </row>
-    <row r="55" spans="1:15" s="74" customFormat="1" ht="121.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" s="74" customFormat="1" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A55" s="71">
         <v>52</v>
       </c>
       <c r="B55" s="72" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="C55" s="55" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="D55" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E55" s="50" t="s">
-        <v>212</v>
+        <v>66</v>
+      </c>
+      <c r="E55" s="51" t="s">
+        <v>180</v>
       </c>
       <c r="F55" s="77" t="s">
-        <v>213</v>
-      </c>
-      <c r="G55" s="50" t="s">
-        <v>200</v>
+        <v>181</v>
+      </c>
+      <c r="G55" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="H55" s="78" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I55" s="79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J55" s="78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="K55" s="81" t="s">
-        <v>214</v>
-      </c>
-      <c r="L55" s="50" t="s">
-        <v>140</v>
+        <v>182</v>
+      </c>
+      <c r="L55" s="51" t="s">
+        <v>282</v>
       </c>
       <c r="M55" s="33"/>
       <c r="N55" s="33"/>
       <c r="O55" s="40"/>
     </row>
-    <row r="56" spans="1:15" s="74" customFormat="1" ht="175.5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" s="74" customFormat="1" ht="171.6" x14ac:dyDescent="0.25">
       <c r="A56" s="71">
         <v>53</v>
       </c>
       <c r="B56" s="72" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="C56" s="55" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="D56" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E56" s="50" t="s">
-        <v>216</v>
+        <v>66</v>
+      </c>
+      <c r="E56" s="51" t="s">
+        <v>184</v>
       </c>
       <c r="F56" s="42" t="s">
-        <v>217</v>
-      </c>
-      <c r="G56" s="50" t="s">
-        <v>200</v>
+        <v>185</v>
+      </c>
+      <c r="G56" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="H56" s="80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I56" s="80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J56" s="80">
-        <f t="shared" ref="J56:J57" si="9">IF(H56="NA","NA",IF(H56="Yes",10,-10))</f>
+        <f t="shared" ref="J56:J57" si="10">IF(H56="NA","NA",IF(H56="Yes",10,-10))</f>
         <v>10</v>
       </c>
       <c r="K56" s="81" t="s">
-        <v>218</v>
-      </c>
-      <c r="L56" s="50" t="s">
-        <v>140</v>
+        <v>186</v>
+      </c>
+      <c r="L56" s="51" t="s">
+        <v>282</v>
       </c>
       <c r="M56" s="33"/>
       <c r="N56" s="33"/>
       <c r="O56" s="40"/>
     </row>
-    <row r="57" spans="1:15" s="74" customFormat="1" ht="94.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" s="74" customFormat="1" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A57" s="71">
         <v>54</v>
       </c>
       <c r="B57" s="72" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="C57" s="55" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="D57" s="55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E57" s="42" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="F57" s="42" t="s">
-        <v>219</v>
-      </c>
-      <c r="G57" s="50" t="s">
-        <v>200</v>
+        <v>187</v>
+      </c>
+      <c r="G57" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="H57" s="80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I57" s="80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J57" s="80">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="K57" s="81"/>
-      <c r="L57" s="50" t="s">
-        <v>140</v>
+      <c r="L57" s="51" t="s">
+        <v>282</v>
       </c>
       <c r="M57" s="33"/>
       <c r="N57" s="33"/>
       <c r="O57" s="40"/>
     </row>
-    <row r="58" spans="1:15" s="82" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" s="82" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="61" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B58" s="62"/>
       <c r="C58" s="63"/>
       <c r="D58" s="63"/>
       <c r="E58" s="64" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F58" s="64"/>
       <c r="G58" s="64"/>
@@ -5326,95 +5110,95 @@
       <c r="N58" s="68"/>
       <c r="O58" s="69"/>
     </row>
-    <row r="59" spans="1:15" s="83" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" s="83" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A59" s="71">
         <v>55</v>
       </c>
       <c r="B59" s="72" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="C59" s="55" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="D59" s="55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E59" s="42" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="F59" s="42" t="s">
-        <v>223</v>
-      </c>
-      <c r="G59" s="50" t="s">
-        <v>200</v>
+        <v>191</v>
+      </c>
+      <c r="G59" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="H59" s="80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I59" s="80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J59" s="80">
-        <f t="shared" ref="J59:J60" si="10">IF(H59="NA","NA",IF(H59="Yes",10,-10))</f>
+        <f t="shared" ref="J59:J60" si="11">IF(H59="NA","NA",IF(H59="Yes",10,-10))</f>
         <v>10</v>
       </c>
       <c r="K59" s="42"/>
       <c r="L59" s="33" t="s">
-        <v>224</v>
+        <v>291</v>
       </c>
       <c r="M59" s="33"/>
       <c r="N59" s="33"/>
       <c r="O59" s="40"/>
     </row>
-    <row r="60" spans="1:15" s="74" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" s="74" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A60" s="71">
         <v>56</v>
       </c>
       <c r="B60" s="72" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="C60" s="55" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="D60" s="55" t="s">
-        <v>99</v>
-      </c>
-      <c r="E60" s="50" t="s">
-        <v>227</v>
-      </c>
-      <c r="F60" s="50" t="s">
-        <v>228</v>
-      </c>
-      <c r="G60" s="50" t="s">
-        <v>200</v>
+        <v>91</v>
+      </c>
+      <c r="E60" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="F60" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="G60" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="H60" s="80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I60" s="80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J60" s="80">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="K60" s="56"/>
-      <c r="L60" s="50" t="s">
-        <v>229</v>
-      </c>
-      <c r="M60" s="50"/>
-      <c r="N60" s="50"/>
+      <c r="L60" s="51" t="s">
+        <v>292</v>
+      </c>
+      <c r="M60" s="51"/>
+      <c r="N60" s="51"/>
       <c r="O60" s="57"/>
     </row>
-    <row r="61" spans="1:15" s="70" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" s="70" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A61" s="61" t="s">
-        <v>230</v>
+        <v>196</v>
       </c>
       <c r="B61" s="62"/>
       <c r="C61" s="62"/>
       <c r="D61" s="62"/>
       <c r="E61" s="64" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F61" s="64"/>
       <c r="G61" s="64"/>
@@ -5430,304 +5214,304 @@
       <c r="N61" s="64"/>
       <c r="O61" s="69"/>
     </row>
-    <row r="62" spans="1:15" s="74" customFormat="1" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" s="74" customFormat="1" ht="66" x14ac:dyDescent="0.25">
       <c r="A62" s="71">
         <v>57</v>
       </c>
       <c r="B62" s="72" t="s">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="C62" s="55" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="D62" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E62" s="50" t="s">
-        <v>233</v>
-      </c>
-      <c r="F62" s="50" t="s">
-        <v>233</v>
+        <v>66</v>
+      </c>
+      <c r="E62" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="F62" s="51" t="s">
+        <v>199</v>
       </c>
       <c r="G62" s="35" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I62" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J62" s="37">
         <f>IF(H62="NA","NA",IF(H62="Critical",-10,IF(H62="Yes",10,IF(I62=1,-2,IF(I62=2,-4,IF(I62=3,-6,IF(I62=4,-8,-10)))))))</f>
         <v>10</v>
       </c>
       <c r="K62" s="56" t="s">
-        <v>234</v>
-      </c>
-      <c r="L62" s="50" t="s">
-        <v>140</v>
+        <v>200</v>
+      </c>
+      <c r="L62" s="51" t="s">
+        <v>282</v>
       </c>
       <c r="M62" s="86"/>
       <c r="N62" s="86"/>
       <c r="O62" s="57"/>
     </row>
-    <row r="63" spans="1:15" s="74" customFormat="1" ht="54" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" s="74" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A63" s="71">
         <v>58</v>
       </c>
       <c r="B63" s="72" t="s">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="C63" s="55" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="D63" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="E63" s="50" t="s">
-        <v>236</v>
-      </c>
-      <c r="F63" s="50" t="s">
-        <v>236</v>
+        <v>66</v>
+      </c>
+      <c r="E63" s="51" t="s">
+        <v>202</v>
+      </c>
+      <c r="F63" s="51" t="s">
+        <v>202</v>
       </c>
       <c r="G63" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="H63" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="H63" s="36" t="s">
-        <v>71</v>
-      </c>
       <c r="I63" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J63" s="38">
-        <f t="shared" ref="J63:J65" si="11">IF(H63="NA","NA",IF(H63="Yes",10,0))</f>
+        <f t="shared" ref="J63:J65" si="12">IF(H63="NA","NA",IF(H63="Yes",10,0))</f>
         <v>10</v>
       </c>
       <c r="K63" s="56" t="s">
-        <v>237</v>
-      </c>
-      <c r="L63" s="50" t="s">
-        <v>238</v>
-      </c>
-      <c r="M63" s="50"/>
-      <c r="N63" s="50"/>
+        <v>203</v>
+      </c>
+      <c r="L63" s="51" t="s">
+        <v>293</v>
+      </c>
+      <c r="M63" s="51"/>
+      <c r="N63" s="51"/>
       <c r="O63" s="57"/>
     </row>
-    <row r="64" spans="1:15" s="74" customFormat="1" ht="54" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" s="74" customFormat="1" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A64" s="71">
         <v>59</v>
       </c>
       <c r="B64" s="72" t="s">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="C64" s="55" t="s">
-        <v>239</v>
+        <v>204</v>
       </c>
       <c r="D64" s="55" t="s">
-        <v>99</v>
-      </c>
-      <c r="E64" s="50" t="s">
-        <v>240</v>
-      </c>
-      <c r="F64" s="50" t="s">
-        <v>240</v>
+        <v>91</v>
+      </c>
+      <c r="E64" s="51" t="s">
+        <v>205</v>
+      </c>
+      <c r="F64" s="51" t="s">
+        <v>205</v>
       </c>
       <c r="G64" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="H64" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="H64" s="36" t="s">
-        <v>71</v>
-      </c>
       <c r="I64" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J64" s="38">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="K64" s="56" t="s">
-        <v>241</v>
+        <v>206</v>
       </c>
       <c r="L64" s="86" t="s">
-        <v>242</v>
-      </c>
-      <c r="M64" s="50"/>
-      <c r="N64" s="50"/>
+        <v>294</v>
+      </c>
+      <c r="M64" s="51"/>
+      <c r="N64" s="51"/>
       <c r="O64" s="57"/>
     </row>
-    <row r="65" spans="1:15" s="74" customFormat="1" ht="54" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" s="74" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A65" s="71">
         <v>60</v>
       </c>
       <c r="B65" s="72" t="s">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="C65" s="55" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="D65" s="55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E65" s="86" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="F65" s="86" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="G65" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="H65" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="H65" s="36" t="s">
-        <v>71</v>
-      </c>
       <c r="I65" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J65" s="38">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
-      <c r="K65" s="50" t="s">
-        <v>245</v>
+      <c r="K65" s="51" t="s">
+        <v>209</v>
       </c>
       <c r="L65" s="86" t="s">
-        <v>246</v>
+        <v>295</v>
       </c>
       <c r="M65" s="86"/>
       <c r="N65" s="86"/>
       <c r="O65" s="57"/>
     </row>
-    <row r="66" spans="1:15" s="74" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15" s="74" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A66" s="71">
         <v>61</v>
       </c>
       <c r="B66" s="72" t="s">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="C66" s="55" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="D66" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E66" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="F66" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="G66" s="50" t="s">
-        <v>200</v>
+        <v>95</v>
+      </c>
+      <c r="E66" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="F66" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="G66" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="H66" s="78" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I66" s="87" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J66" s="80">
         <f>IF(H66="NA","NA",IF(H66="Yes",10,-5))</f>
         <v>10</v>
       </c>
-      <c r="K66" s="50" t="s">
-        <v>249</v>
+      <c r="K66" s="51" t="s">
+        <v>212</v>
       </c>
       <c r="L66" s="86" t="s">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="M66" s="33"/>
       <c r="N66" s="33"/>
       <c r="O66" s="57"/>
     </row>
-    <row r="67" spans="1:15" s="74" customFormat="1" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" s="74" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A67" s="71">
         <v>62</v>
       </c>
       <c r="B67" s="72" t="s">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="C67" s="55" t="s">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="D67" s="55" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E67" s="56" t="s">
-        <v>252</v>
+        <v>214</v>
       </c>
       <c r="F67" s="56" t="s">
-        <v>252</v>
+        <v>214</v>
       </c>
       <c r="G67" s="88" t="s">
-        <v>253</v>
+        <v>215</v>
       </c>
       <c r="H67" s="89" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I67" s="87" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J67" s="78">
-        <f t="shared" ref="J67" si="12">IF(H67="NA","NA",IF(H67="Yes",10,0))</f>
+        <f t="shared" ref="J67" si="13">IF(H67="NA","NA",IF(H67="Yes",10,0))</f>
         <v>10</v>
       </c>
-      <c r="K67" s="50"/>
+      <c r="K67" s="51"/>
       <c r="L67" s="33" t="s">
-        <v>254</v>
+        <v>297</v>
       </c>
       <c r="M67" s="33"/>
       <c r="N67" s="33"/>
       <c r="O67" s="57"/>
     </row>
-    <row r="68" spans="1:15" s="74" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" s="74" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A68" s="71">
         <v>63</v>
       </c>
       <c r="B68" s="72" t="s">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="C68" s="55" t="s">
-        <v>255</v>
+        <v>216</v>
       </c>
       <c r="D68" s="55" t="s">
-        <v>99</v>
-      </c>
-      <c r="E68" s="50" t="s">
-        <v>256</v>
-      </c>
-      <c r="F68" s="50" t="s">
-        <v>256</v>
+        <v>91</v>
+      </c>
+      <c r="E68" s="51" t="s">
+        <v>217</v>
+      </c>
+      <c r="F68" s="51" t="s">
+        <v>217</v>
       </c>
       <c r="G68" s="88" t="s">
         <v>6</v>
       </c>
       <c r="H68" s="79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I68" s="79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J68" s="79" t="s">
-        <v>72</v>
-      </c>
-      <c r="K68" s="50"/>
-      <c r="L68" s="50" t="s">
-        <v>257</v>
-      </c>
-      <c r="M68" s="50"/>
-      <c r="N68" s="50"/>
+        <v>71</v>
+      </c>
+      <c r="K68" s="51"/>
+      <c r="L68" s="51" t="s">
+        <v>298</v>
+      </c>
+      <c r="M68" s="51"/>
+      <c r="N68" s="51"/>
       <c r="O68" s="57"/>
     </row>
-    <row r="69" spans="1:15" s="70" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" s="70" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="90" t="s">
-        <v>258</v>
+        <v>218</v>
       </c>
       <c r="B69" s="91"/>
       <c r="C69" s="92"/>
       <c r="D69" s="93"/>
       <c r="E69" s="92" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F69" s="92"/>
       <c r="G69" s="92"/>
@@ -5745,45 +5529,45 @@
     </row>
   </sheetData>
   <dataValidations count="12">
-    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" error="Invalid Entry." prompt="Pls select from drop down menu only." sqref="I69 I66:I67 I6:I15 I40:I41 I37 I26:I28 I61 I17:I19 I30:I35" xr:uid="{FD416413-45ED-4566-BEC1-2C312BBC2C8C}">
-      <formula1>"1,2,3,4,&gt;4,NA"</formula1>
-      <formula2>0</formula2>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid Entry" prompt="Please select from the drop down menu only." sqref="I43:I46 I36 I62 I38:I39" xr:uid="{1AB70794-EC85-4F5E-8520-47075C42FFDC}">
+      <formula1>"1,2,3,4, &gt;4, NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Invaild Entry." prompt="Pls select from drop down menu only." sqref="H69 H61 H6:H15 H17:H18 H37 H47 H67 H58 H26:H35 H40:H41" xr:uid="{57901F32-E0D7-4D48-AC95-5AF3C767327F}">
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" error="Invalid Entry" prompt="Please select from the drop down menu only." sqref="H36 H42" xr:uid="{F8B27563-3189-4AE4-9139-937E81463807}">
+      <formula1>"Yes,No,Critical,NA"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invaild Entry." prompt="Pls select from drop down menu only." sqref="H2:H5 H16 H63:H65 H20:H25" xr:uid="{B6959F41-6614-4978-B3BB-A5B8C8B60851}">
       <formula1>"Yes,No,NA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" error="Invalid Entry" prompt="Please select from the drop down menu only." sqref="H43:H46 H66 H48 H38:H39 H62 H50:H55" xr:uid="{91067269-F6E6-46BB-90F2-571460894FFF}">
-      <formula1>"Yes,No,NA"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I42" xr:uid="{EFAF58D8-C7C1-4113-86DD-24B255EE745E}">
+      <formula1>"1,2,3,4,5,6,7,8,9,10,NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Invaild Entry." prompt="Pls select from drop down menu only." sqref="H19" xr:uid="{A3164144-8750-499C-AF14-3F4A2A9FBE61}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I20:I25 I63:I65 I48 I16 I2:I5 I50:I55" xr:uid="{3EBED7EB-6440-47B9-B461-8209DADECFFB}">
+      <formula1>"1,2,3,4,&gt;4,NA"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59:H60 H56:H57 H49" xr:uid="{94DAF8F8-7E91-49C8-8F9D-5596E07A664A}">
+      <formula1>"Yes, No, NA, Critical"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I59:I60 I56:I57 I49" xr:uid="{3606CBF3-BDAF-43C9-82AB-6058A469D75C}">
+      <formula1>"1,2,3,4,GT4,NA"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" error="Invalid Entry." prompt="Pls select from drop down menu only." sqref="I58 I47 I29" xr:uid="{A381A3BB-4832-476F-B366-2CCDD74A4CFC}">
+      <formula1>"&lt;70%,NA"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Invaild Entry." prompt="Pls select from drop down menu only." sqref="H19" xr:uid="{F040649C-5455-48B4-915B-C99F0132CD01}">
       <formula1>"Yes,No,Critical,NA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" error="Invalid Entry." prompt="Pls select from drop down menu only." sqref="I58 I47 I29" xr:uid="{157AEAA9-C6BE-4984-A88B-4FBC836CA070}">
-      <formula1>"&lt;70%,NA"</formula1>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" error="Invalid Entry" prompt="Please select from the drop down menu only." sqref="H43:H46 H66 H48 H38:H39 H62 H50:H55" xr:uid="{2BFAD3BA-727C-4E63-87E1-49FACAA64C4F}">
+      <formula1>"Yes,No,NA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I59:I60 I56:I57 I49" xr:uid="{6399D2D9-A624-446A-804D-323323D5D89D}">
-      <formula1>"1,2,3,4,GT4,NA"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H59:H60 H56:H57 H49" xr:uid="{5C1D9A42-022F-406A-8063-419F6486471B}">
-      <formula1>"Yes, No, NA, Critical"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I20:I25 I63:I65 I48 I16 I2:I5 I50:I55" xr:uid="{5660564C-E0AC-484F-90CC-ED565CB3096E}">
-      <formula1>"1,2,3,4,&gt;4,NA"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I42" xr:uid="{39D4C858-4F91-4DA2-BEDE-A5CAA686011E}">
-      <formula1>"1,2,3,4,5,6,7,8,9,10,NA"</formula1>
-    </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invaild Entry." prompt="Pls select from drop down menu only." sqref="H2:H5 H16 H63:H65 H20:H25" xr:uid="{2E4DF1CA-0B1C-4628-A91D-ACD1AEE986DA}">
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Invaild Entry." prompt="Pls select from drop down menu only." sqref="H69 H61 H6:H15 H17:H18 H37 H47 H67 H58 H26:H35 H40:H41" xr:uid="{7EDF1666-6AC0-41BB-94F2-3A5764EADDEC}">
       <formula1>"Yes,No,NA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" error="Invalid Entry" prompt="Please select from the drop down menu only." sqref="H36 H42" xr:uid="{F1D1880F-E392-4BDC-B1C6-B793FDB72709}">
-      <formula1>"Yes,No,Critical,NA"</formula1>
-    </dataValidation>
-    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Invalid Entry" prompt="Please select from the drop down menu only." sqref="I43:I46 I36 I62 I38:I39" xr:uid="{D978FE00-9F9D-4B5C-AC40-12030D806B41}">
-      <formula1>"1,2,3,4, &gt;4, NA"</formula1>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" error="Invalid Entry." prompt="Pls select from drop down menu only." sqref="I69 I66:I67 I6:I15 I40:I41 I37 I26:I28 I61 I17:I19 I30:I35" xr:uid="{806E6B37-3294-48BC-B5ED-4B6E2320E833}">
+      <formula1>"1,2,3,4,&gt;4,NA"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5793,127 +5577,127 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCBB10ED-61AB-47E0-BEF5-1EF8BDC7F3FE}">
-  <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D599F91-A01D-4D1C-B538-B94856059891}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:AB16"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" style="101" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.25" style="101" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.75" style="101" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.625" style="101" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.25" style="101" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="26.875" style="101" customWidth="1"/>
-    <col min="8" max="8" width="54.75" style="101" customWidth="1"/>
-    <col min="9" max="9" width="42.75" style="101" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.25" style="101" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.25" style="101" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.625" style="101" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.625" style="101" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5" style="101" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5" style="101" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.75" style="101" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.5" style="101" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.25" style="101" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.5" style="101" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="22" style="101" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.25" style="101" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.5" style="101" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="28.625" style="101" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="28.125" style="101" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="18.875" style="101" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="21.125" style="101" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="24.125" style="101" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="8" style="101"/>
+    <col min="1" max="1" width="18.33203125" style="140" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" style="140" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="140" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" style="140" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" style="140" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="30.6640625" style="140" customWidth="1"/>
+    <col min="8" max="8" width="62.5546875" style="140" customWidth="1"/>
+    <col min="9" max="9" width="48.88671875" style="140" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="140" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.109375" style="140" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.88671875" style="140" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27" style="140" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" style="140" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.5546875" style="140" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" style="140" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.88671875" style="140" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.88671875" style="140" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.33203125" style="140" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="25.109375" style="140" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.88671875" style="140" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="23.44140625" style="140" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="32.6640625" style="140" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="32.109375" style="140" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.5546875" style="140" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.109375" style="140" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="27.5546875" style="140" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.109375" style="140"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="100" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="139" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
-        <v>259</v>
+        <v>219</v>
       </c>
       <c r="B1" s="99" t="s">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="C1" s="99" t="s">
-        <v>261</v>
+        <v>221</v>
       </c>
       <c r="D1" s="99" t="s">
-        <v>262</v>
+        <v>222</v>
       </c>
       <c r="E1" s="99" t="s">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="F1" s="99" t="s">
         <v>10</v>
       </c>
       <c r="G1" s="99" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="H1" s="99" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I1" s="99" t="s">
-        <v>265</v>
+        <v>225</v>
       </c>
       <c r="J1" s="99" t="s">
-        <v>266</v>
+        <v>226</v>
       </c>
       <c r="K1" s="99" t="s">
-        <v>267</v>
+        <v>227</v>
       </c>
       <c r="L1" s="99" t="s">
-        <v>268</v>
+        <v>228</v>
       </c>
       <c r="M1" s="99" t="s">
-        <v>269</v>
+        <v>229</v>
       </c>
       <c r="N1" s="99" t="s">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="O1" s="99" t="s">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="P1" s="99" t="s">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="Q1" s="99" t="s">
-        <v>273</v>
+        <v>233</v>
       </c>
       <c r="R1" s="99" t="s">
-        <v>274</v>
+        <v>234</v>
       </c>
       <c r="S1" s="99" t="s">
-        <v>275</v>
+        <v>235</v>
       </c>
       <c r="T1" s="99" t="s">
-        <v>276</v>
+        <v>236</v>
       </c>
       <c r="U1" s="99" t="s">
-        <v>277</v>
+        <v>237</v>
       </c>
       <c r="V1" s="99" t="s">
-        <v>278</v>
+        <v>238</v>
       </c>
       <c r="W1" s="99" t="s">
-        <v>279</v>
+        <v>239</v>
       </c>
       <c r="X1" s="99" t="s">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="Y1" s="99" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="Z1" s="99" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="AA1" s="99" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="AB1" s="99" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="22"/>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -5943,7 +5727,7 @@
       <c r="AA2" s="22"/>
       <c r="AB2" s="22"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="22"/>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -5973,7 +5757,7 @@
       <c r="AA3" s="22"/>
       <c r="AB3" s="22"/>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -6003,7 +5787,7 @@
       <c r="AA4" s="22"/>
       <c r="AB4" s="22"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="22"/>
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
@@ -6033,7 +5817,7 @@
       <c r="AA5" s="22"/>
       <c r="AB5" s="22"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="22"/>
       <c r="B6" s="22"/>
       <c r="C6" s="22"/>
@@ -6063,7 +5847,7 @@
       <c r="AA6" s="22"/>
       <c r="AB6" s="22"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="22"/>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
@@ -6093,7 +5877,7 @@
       <c r="AA7" s="22"/>
       <c r="AB7" s="22"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="22"/>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
@@ -6123,7 +5907,7 @@
       <c r="AA8" s="22"/>
       <c r="AB8" s="22"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="22"/>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
@@ -6153,7 +5937,7 @@
       <c r="AA9" s="22"/>
       <c r="AB9" s="22"/>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="22"/>
       <c r="B10" s="22"/>
       <c r="C10" s="22"/>
@@ -6183,7 +5967,7 @@
       <c r="AA10" s="22"/>
       <c r="AB10" s="22"/>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="22"/>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
@@ -6213,6 +5997,156 @@
       <c r="AA11" s="22"/>
       <c r="AB11" s="22"/>
     </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="22"/>
+      <c r="U12" s="22"/>
+      <c r="V12" s="22"/>
+      <c r="W12" s="22"/>
+      <c r="X12" s="22"/>
+      <c r="Y12" s="22"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="22"/>
+      <c r="AB12" s="22"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="22"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="22"/>
+      <c r="AB14" s="22"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="22"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="22"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="22"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6220,335 +6154,137 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B1C4439-B92D-47B6-B553-4AB169B9F213}">
-  <sheetPr codeName="Sheet5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26C0E42-6A78-4053-9433-7ED1F4260C2F}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="6.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8" style="1"/>
+    <col min="1" max="1" width="5.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.3">
-      <c r="A1" s="102" t="s">
-        <v>285</v>
-      </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="104"/>
-    </row>
-    <row r="2" spans="1:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="104"/>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="104"/>
-    </row>
-    <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="105" t="s">
-        <v>286</v>
-      </c>
-      <c r="B3" s="141" t="s">
-        <v>287</v>
-      </c>
-      <c r="C3" s="141" t="s">
-        <v>288</v>
-      </c>
-      <c r="D3" s="107" t="s">
-        <v>289</v>
-      </c>
-      <c r="E3" s="141" t="s">
-        <v>290</v>
-      </c>
-      <c r="F3" s="107" t="s">
-        <v>291</v>
-      </c>
-      <c r="G3" s="107" t="s">
-        <v>292</v>
-      </c>
-      <c r="H3" s="142" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="109">
-        <v>1</v>
-      </c>
-      <c r="B4" s="110" t="s">
-        <v>350</v>
-      </c>
-      <c r="C4" s="110" t="s">
-        <v>351</v>
-      </c>
-      <c r="D4" s="110" t="s">
-        <v>352</v>
-      </c>
-      <c r="E4" s="111" t="s">
-        <v>353</v>
-      </c>
-      <c r="F4" s="111" t="s">
-        <v>352</v>
-      </c>
-      <c r="G4" s="111" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" s="112" t="s">
-        <v>354</v>
-      </c>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="100" t="s">
+        <v>245</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="102"/>
+    </row>
+    <row r="2" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="102"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="102"/>
+    </row>
+    <row r="3" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="103" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" s="104" t="s">
+        <v>247</v>
+      </c>
+      <c r="C3" s="104" t="s">
+        <v>248</v>
+      </c>
+      <c r="D3" s="105" t="s">
+        <v>249</v>
+      </c>
+      <c r="E3" s="104" t="s">
+        <v>250</v>
+      </c>
+      <c r="F3" s="105" t="s">
+        <v>251</v>
+      </c>
+      <c r="G3" s="105" t="s">
+        <v>252</v>
+      </c>
+      <c r="H3" s="106" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="107"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="110"/>
       <c r="I4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="109">
-        <v>2</v>
-      </c>
-      <c r="B5" s="110" t="s">
-        <v>355</v>
-      </c>
-      <c r="C5" s="110" t="s">
-        <v>356</v>
-      </c>
-      <c r="D5" s="110" t="s">
-        <v>352</v>
-      </c>
-      <c r="E5" s="111" t="s">
-        <v>353</v>
-      </c>
-      <c r="F5" s="111" t="s">
-        <v>352</v>
-      </c>
-      <c r="G5" s="111" t="s">
-        <v>71</v>
-      </c>
-      <c r="H5" s="112" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="109">
-        <v>3</v>
-      </c>
-      <c r="B6" s="110" t="s">
-        <v>357</v>
-      </c>
-      <c r="C6" s="110" t="s">
-        <v>358</v>
-      </c>
-      <c r="D6" s="110" t="s">
-        <v>352</v>
-      </c>
-      <c r="E6" s="111" t="s">
-        <v>353</v>
-      </c>
-      <c r="F6" s="111" t="s">
-        <v>352</v>
-      </c>
-      <c r="G6" s="111" t="s">
-        <v>71</v>
-      </c>
-      <c r="H6" s="112" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="109">
-        <v>4</v>
-      </c>
-      <c r="B7" s="110" t="s">
-        <v>359</v>
-      </c>
-      <c r="C7" s="110" t="s">
-        <v>360</v>
-      </c>
-      <c r="D7" s="110" t="s">
-        <v>361</v>
-      </c>
-      <c r="E7" s="111" t="s">
-        <v>353</v>
-      </c>
-      <c r="F7" s="111" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="111" t="s">
-        <v>71</v>
-      </c>
-      <c r="H7" s="112" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="109">
-        <v>5</v>
-      </c>
-      <c r="B8" s="110" t="s">
-        <v>362</v>
-      </c>
-      <c r="C8" s="110" t="s">
-        <v>363</v>
-      </c>
-      <c r="D8" s="110" t="s">
-        <v>352</v>
-      </c>
-      <c r="E8" s="111" t="s">
-        <v>353</v>
-      </c>
-      <c r="F8" s="111" t="s">
-        <v>352</v>
-      </c>
-      <c r="G8" s="111" t="s">
-        <v>71</v>
-      </c>
-      <c r="H8" s="112" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="109">
-        <v>6</v>
-      </c>
-      <c r="B9" s="110" t="s">
-        <v>364</v>
-      </c>
-      <c r="C9" s="110" t="s">
-        <v>365</v>
-      </c>
-      <c r="D9" s="110" t="s">
-        <v>352</v>
-      </c>
-      <c r="E9" s="111" t="s">
-        <v>353</v>
-      </c>
-      <c r="F9" s="111" t="s">
-        <v>352</v>
-      </c>
-      <c r="G9" s="111" t="s">
-        <v>71</v>
-      </c>
-      <c r="H9" s="112" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="109">
-        <v>7</v>
-      </c>
-      <c r="B10" s="110" t="s">
-        <v>366</v>
-      </c>
-      <c r="C10" s="110" t="s">
-        <v>367</v>
-      </c>
-      <c r="D10" s="110" t="s">
-        <v>352</v>
-      </c>
-      <c r="E10" s="111" t="s">
-        <v>353</v>
-      </c>
-      <c r="F10" s="111" t="s">
-        <v>352</v>
-      </c>
-      <c r="G10" s="111" t="s">
-        <v>71</v>
-      </c>
-      <c r="H10" s="112" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="109">
-        <v>8</v>
-      </c>
-      <c r="B11" s="110" t="s">
-        <v>368</v>
-      </c>
-      <c r="C11" s="110" t="s">
-        <v>369</v>
-      </c>
-      <c r="D11" s="110" t="s">
-        <v>352</v>
-      </c>
-      <c r="E11" s="111" t="s">
-        <v>353</v>
-      </c>
-      <c r="F11" s="111" t="s">
-        <v>352</v>
-      </c>
-      <c r="G11" s="111" t="s">
-        <v>71</v>
-      </c>
-      <c r="H11" s="112" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="109">
-        <v>9</v>
-      </c>
-      <c r="B12" s="110" t="s">
-        <v>370</v>
-      </c>
-      <c r="C12" s="110" t="s">
-        <v>371</v>
-      </c>
-      <c r="D12" s="110" t="s">
-        <v>352</v>
-      </c>
-      <c r="E12" s="111" t="s">
-        <v>353</v>
-      </c>
-      <c r="F12" s="111" t="s">
-        <v>352</v>
-      </c>
-      <c r="G12" s="111" t="s">
-        <v>71</v>
-      </c>
-      <c r="H12" s="112" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="113">
-        <v>10</v>
-      </c>
-      <c r="B13" s="114" t="s">
-        <v>372</v>
-      </c>
-      <c r="C13" s="114" t="s">
-        <v>373</v>
-      </c>
-      <c r="D13" s="114" t="s">
-        <v>352</v>
-      </c>
-      <c r="E13" s="115" t="s">
-        <v>353</v>
-      </c>
-      <c r="F13" s="115" t="s">
-        <v>352</v>
-      </c>
-      <c r="G13" s="115" t="s">
-        <v>71</v>
-      </c>
-      <c r="H13" s="116" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="C14" s="117"/>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="107"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="110"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="107"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="109"/>
+      <c r="H6" s="110"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="107"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="110"/>
+    </row>
+    <row r="8" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="111"/>
+      <c r="B8" s="112"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="113"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="114"/>
+    </row>
+    <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C10" s="115"/>
+    </row>
+    <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C11" s="115"/>
+    </row>
+    <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C12" s="115"/>
+    </row>
+    <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C13" s="115"/>
+    </row>
+    <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="C14" s="115"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
@@ -6559,331 +6295,186 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13A7CC56-8D6E-4D9C-B8E8-30827C7B7966}">
-  <sheetPr codeName="Sheet6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92EBE374-5B4E-433D-B94A-B19751C4F58C}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8" style="1"/>
+    <col min="1" max="1" width="7.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="10.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="118" t="s">
-        <v>294</v>
-      </c>
-      <c r="B1" s="118"/>
-    </row>
-    <row r="2" spans="1:6" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="116" t="s">
+        <v>254</v>
+      </c>
+      <c r="B1" s="116"/>
+    </row>
+    <row r="2" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C2" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="105" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="106" t="s">
-        <v>290</v>
-      </c>
-      <c r="C3" s="106" t="s">
-        <v>296</v>
-      </c>
-      <c r="D3" s="106" t="s">
-        <v>267</v>
-      </c>
-      <c r="E3" s="107" t="s">
-        <v>297</v>
-      </c>
-      <c r="F3" s="108" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="119">
-        <v>1</v>
-      </c>
-      <c r="B4" s="120" t="s">
-        <v>324</v>
-      </c>
-      <c r="C4" s="110" t="s">
-        <v>325</v>
-      </c>
-      <c r="D4" s="121" t="s">
-        <v>326</v>
-      </c>
-      <c r="E4" s="122" t="s">
-        <v>71</v>
-      </c>
-      <c r="F4" s="123" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="119">
-        <v>2</v>
-      </c>
-      <c r="B5" s="120" t="s">
-        <v>327</v>
-      </c>
-      <c r="C5" s="110" t="s">
-        <v>328</v>
-      </c>
-      <c r="D5" s="121" t="s">
-        <v>329</v>
-      </c>
-      <c r="E5" s="122" t="s">
-        <v>71</v>
-      </c>
-      <c r="F5" s="123" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="119">
-        <v>3</v>
-      </c>
-      <c r="B6" s="120" t="s">
-        <v>327</v>
-      </c>
-      <c r="C6" s="110" t="s">
-        <v>330</v>
-      </c>
-      <c r="D6" s="121" t="s">
-        <v>329</v>
-      </c>
-      <c r="E6" s="122" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="123" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="119">
-        <v>4</v>
-      </c>
-      <c r="B7" s="120" t="s">
-        <v>327</v>
-      </c>
-      <c r="C7" s="110" t="s">
-        <v>331</v>
-      </c>
-      <c r="D7" s="121" t="s">
-        <v>332</v>
-      </c>
-      <c r="E7" s="122" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="123" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="119">
-        <v>5</v>
-      </c>
-      <c r="B8" s="120" t="s">
-        <v>324</v>
-      </c>
-      <c r="C8" s="110" t="s">
-        <v>333</v>
-      </c>
-      <c r="D8" s="121" t="s">
-        <v>334</v>
-      </c>
-      <c r="E8" s="122" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" s="123" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="119">
-        <v>6</v>
-      </c>
-      <c r="B9" s="124" t="s">
-        <v>324</v>
-      </c>
-      <c r="C9" s="125" t="s">
-        <v>335</v>
-      </c>
-      <c r="D9" s="126" t="s">
-        <v>336</v>
-      </c>
-      <c r="E9" s="122" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" s="123" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="119">
-        <v>7</v>
-      </c>
-      <c r="B10" s="124" t="s">
-        <v>324</v>
-      </c>
-      <c r="C10" s="125" t="s">
-        <v>337</v>
-      </c>
-      <c r="D10" s="126" t="s">
-        <v>338</v>
-      </c>
-      <c r="E10" s="122" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="123" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="119">
-        <v>8</v>
-      </c>
-      <c r="B11" s="124" t="s">
-        <v>327</v>
-      </c>
-      <c r="C11" s="125" t="s">
-        <v>339</v>
-      </c>
-      <c r="D11" s="126" t="s">
-        <v>340</v>
-      </c>
-      <c r="E11" s="122" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="123" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="119">
-        <v>9</v>
-      </c>
-      <c r="B12" s="124" t="s">
-        <v>327</v>
-      </c>
-      <c r="C12" s="125" t="s">
-        <v>341</v>
-      </c>
-      <c r="D12" s="126" t="s">
-        <v>342</v>
-      </c>
-      <c r="E12" s="122" t="s">
-        <v>71</v>
-      </c>
-      <c r="F12" s="123" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="119">
-        <v>10</v>
-      </c>
-      <c r="B13" s="124" t="s">
-        <v>327</v>
-      </c>
-      <c r="C13" s="125" t="s">
-        <v>343</v>
-      </c>
-      <c r="D13" s="126" t="s">
-        <v>344</v>
-      </c>
-      <c r="E13" s="122" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="123" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="119">
-        <v>11</v>
-      </c>
-      <c r="B14" s="124" t="s">
-        <v>324</v>
-      </c>
-      <c r="C14" s="125" t="s">
-        <v>345</v>
-      </c>
-      <c r="D14" s="126" t="s">
-        <v>346</v>
-      </c>
-      <c r="E14" s="122" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14" s="123" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="119">
-        <v>12</v>
-      </c>
-      <c r="B15" s="124" t="s">
-        <v>327</v>
-      </c>
-      <c r="C15" s="125" t="s">
-        <v>347</v>
-      </c>
-      <c r="D15" s="126" t="s">
-        <v>348</v>
-      </c>
-      <c r="E15" s="122" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="123" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="127"/>
-      <c r="B16" s="120"/>
-      <c r="C16" s="110"/>
-      <c r="D16" s="128"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="123"/>
-    </row>
-    <row r="17" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="127"/>
-      <c r="B17" s="120"/>
-      <c r="C17" s="110"/>
-      <c r="D17" s="128"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="123"/>
-    </row>
-    <row r="18" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="127"/>
-      <c r="B18" s="120"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="128"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="123"/>
-    </row>
-    <row r="19" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="127"/>
-      <c r="B19" s="124"/>
-      <c r="C19" s="125"/>
-      <c r="D19" s="126"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="123"/>
-    </row>
-    <row r="20" spans="1:6" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="129"/>
-      <c r="B20" s="130"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="131"/>
-      <c r="E20" s="132"/>
-      <c r="F20" s="133"/>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="103" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="104" t="s">
+        <v>250</v>
+      </c>
+      <c r="C3" s="104" t="s">
+        <v>256</v>
+      </c>
+      <c r="D3" s="104" t="s">
+        <v>227</v>
+      </c>
+      <c r="E3" s="105" t="s">
+        <v>257</v>
+      </c>
+      <c r="F3" s="106" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="117"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="121"/>
+    </row>
+    <row r="5" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="117"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="121"/>
+    </row>
+    <row r="6" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="117"/>
+      <c r="B6" s="118"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="121"/>
+    </row>
+    <row r="7" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="121"/>
+    </row>
+    <row r="8" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="117"/>
+      <c r="B8" s="118"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="121"/>
+    </row>
+    <row r="9" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="117"/>
+      <c r="B9" s="122"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="121"/>
+    </row>
+    <row r="10" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="117"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="121"/>
+    </row>
+    <row r="11" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="117"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="123"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="120"/>
+      <c r="F11" s="121"/>
+    </row>
+    <row r="12" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="117"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="123"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="120"/>
+      <c r="F12" s="121"/>
+    </row>
+    <row r="13" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="117"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="120"/>
+      <c r="F13" s="121"/>
+    </row>
+    <row r="14" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="117"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="123"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="121"/>
+    </row>
+    <row r="15" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="117"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="123"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="120"/>
+      <c r="F15" s="121"/>
+    </row>
+    <row r="16" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="125"/>
+      <c r="B16" s="118"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="121"/>
+    </row>
+    <row r="17" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="125"/>
+      <c r="B17" s="118"/>
+      <c r="C17" s="108"/>
+      <c r="D17" s="126"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="121"/>
+    </row>
+    <row r="18" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="125"/>
+      <c r="B18" s="118"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="126"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="121"/>
+    </row>
+    <row r="19" spans="1:6" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="125"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="124"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="121"/>
+    </row>
+    <row r="20" spans="1:6" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="127"/>
+      <c r="B20" s="128"/>
+      <c r="C20" s="112"/>
+      <c r="D20" s="129"/>
+      <c r="E20" s="130"/>
+      <c r="F20" s="131"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6891,50 +6482,50 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A58AEF-D1BF-4CED-B05E-76973D709952}">
-  <sheetPr codeName="Sheet7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC4810F-619B-4C8C-B5EB-D969A4868025}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.375" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8" style="1"/>
+    <col min="1" max="1" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="A1" s="102" t="s">
-        <v>299</v>
-      </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-    </row>
-    <row r="2" spans="1:6" ht="14.25" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="105" t="s">
-        <v>300</v>
-      </c>
-      <c r="B3" s="106" t="s">
-        <v>301</v>
-      </c>
-      <c r="C3" s="107" t="s">
-        <v>302</v>
-      </c>
-      <c r="D3" s="152" t="s">
-        <v>303</v>
-      </c>
-      <c r="E3" s="152"/>
-      <c r="F3" s="153"/>
-    </row>
-    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="154" t="s">
-        <v>304</v>
-      </c>
-      <c r="B4" s="155"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="155"/>
-      <c r="F4" s="156"/>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="100" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+    </row>
+    <row r="2" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="103" t="s">
+        <v>260</v>
+      </c>
+      <c r="B3" s="104" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" s="105" t="s">
+        <v>262</v>
+      </c>
+      <c r="D3" s="149" t="s">
+        <v>263</v>
+      </c>
+      <c r="E3" s="149"/>
+      <c r="F3" s="150"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="151" t="s">
+        <v>264</v>
+      </c>
+      <c r="B4" s="152"/>
+      <c r="C4" s="152"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="152"/>
+      <c r="F4" s="153"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6946,55 +6537,55 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{482D1AD1-A2C9-4B40-938F-CCAF91D14169}">
-  <sheetPr codeName="Sheet8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76FBC820-A8A6-4F39-9F98-C76DB7C4B3A6}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8" style="1"/>
-    <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8" style="1"/>
+    <col min="1" max="1" width="9.109375" style="1"/>
+    <col min="2" max="2" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.3">
-      <c r="A1" s="102" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="105" t="s">
-        <v>290</v>
-      </c>
-      <c r="B3" s="106" t="s">
-        <v>306</v>
-      </c>
-      <c r="C3" s="106" t="s">
-        <v>307</v>
-      </c>
-      <c r="D3" s="108" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="134"/>
-      <c r="B4" s="135"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="136"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="134"/>
-      <c r="B5" s="135"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="136"/>
-    </row>
-    <row r="6" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="137"/>
-      <c r="B6" s="138"/>
-      <c r="C6" s="138"/>
-      <c r="D6" s="139"/>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="100" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="103" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" s="104" t="s">
+        <v>266</v>
+      </c>
+      <c r="C3" s="104" t="s">
+        <v>267</v>
+      </c>
+      <c r="D3" s="106" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="132"/>
+      <c r="B4" s="133"/>
+      <c r="C4" s="133"/>
+      <c r="D4" s="134"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="132"/>
+      <c r="B5" s="133"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="134"/>
+    </row>
+    <row r="6" spans="1:4" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="135"/>
+      <c r="B6" s="136"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="137"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7003,48 +6594,48 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD96CB88-D26F-47CD-8891-C4117652F44B}">
-  <sheetPr codeName="Sheet9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BDFA264-DAEB-43AF-A0E3-60C9713334FB}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8" style="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.3">
-      <c r="A1" s="140" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="105" t="s">
-        <v>310</v>
-      </c>
-      <c r="B3" s="106" t="s">
-        <v>290</v>
-      </c>
-      <c r="C3" s="106" t="s">
-        <v>296</v>
-      </c>
-      <c r="D3" s="106" t="s">
-        <v>311</v>
-      </c>
-      <c r="E3" s="108" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="157"/>
-      <c r="B4" s="158"/>
-      <c r="C4" s="158"/>
-      <c r="D4" s="158"/>
-      <c r="E4" s="159"/>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="138" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="103" t="s">
+        <v>270</v>
+      </c>
+      <c r="B3" s="104" t="s">
+        <v>250</v>
+      </c>
+      <c r="C3" s="104" t="s">
+        <v>256</v>
+      </c>
+      <c r="D3" s="104" t="s">
+        <v>271</v>
+      </c>
+      <c r="E3" s="106" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="154"/>
+      <c r="B4" s="155"/>
+      <c r="C4" s="155"/>
+      <c r="D4" s="155"/>
+      <c r="E4" s="156"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/templates/YesBank/YesBank_Collection_Template_2026-27.xlsx
+++ b/templates/YesBank/YesBank_Collection_Template_2026-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachit Goyal\Downloads\audit-report-generator\templates\YesBank\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF1C5EA-E1DE-40C9-B84A-A71F92BFCE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A60D0A-D72C-426E-94E8-AB69134BD80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E366AD21-7E7D-48B4-B5AD-0A6D4540711A}"/>
   </bookViews>
@@ -25,7 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Agency!$A$1:$O$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Annexure-4'!$A$3:$D$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">KAF!$A$1:$AB$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">KAF!$B$1:$AC$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="315">
   <si>
     <t>YES Bank Collection Agency Audit</t>
   </si>
@@ -1080,7 +1080,10 @@
     <t>Yes, Call intensity was followed by the agency as per COC guidelines</t>
   </si>
   <si>
-    <t>KGAC</t>
+    <t>Sr. No</t>
+  </si>
+  <si>
+    <t>Kumar Gaurav Agarwal &amp; Company</t>
   </si>
 </sst>
 </file>
@@ -1093,7 +1096,7 @@
     <numFmt numFmtId="166" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="167" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1261,6 +1264,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1299,7 +1308,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1516,8 +1525,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="11">
+  <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1529,8 +1579,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1961,6 +2012,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="17" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2011,8 +2072,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="11">
+  <cellStyles count="12">
     <cellStyle name="_Amar's Vehicle_Audit_Report_auto_july_agt_06_Nasik Auto Jan. 07_cv_PIVOT 1_SERIES 2" xfId="7" xr:uid="{80A8BD56-6ED2-42AB-AA86-B312A219BC06}"/>
     <cellStyle name="_Budg based on trend 1_CPC-RPC BSC SEPT-06_Book6_Branch_Metrics_CPA_Final_APR 09  BM UPLOAD_2" xfId="6" xr:uid="{28E173ED-E52B-43E0-9A01-6200B33124B0}"/>
     <cellStyle name="DataPilot Category" xfId="3" xr:uid="{C2EC733E-5CFA-407E-B51E-3AC609C5D00F}"/>
@@ -2020,6 +2084,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 12" xfId="9" xr:uid="{FFDD31A4-3149-42E5-96DD-6A6E1E53F612}"/>
     <cellStyle name="Normal 2" xfId="5" xr:uid="{A6F519D4-B5BB-4C5C-BDDC-95796F400E88}"/>
+    <cellStyle name="Normal 2 3" xfId="11" xr:uid="{F3E4BDBD-6E3C-4888-B20F-65F67C3D77BC}"/>
     <cellStyle name="Normal 3" xfId="10" xr:uid="{42B7EA57-F015-484E-8E89-09920FFF5840}"/>
     <cellStyle name="Normal_DM_1" xfId="4" xr:uid="{47B18B6C-E73C-4527-9963-C930DB66557B}"/>
     <cellStyle name="Normal_Sheet1" xfId="8" xr:uid="{09FDA902-1D9B-48A7-B13B-EDDE10EE22BC}"/>
@@ -2383,14 +2448,14 @@
   <sheetData>
     <row r="1" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="144" t="s">
+      <c r="B2" s="147" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="146"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="148"/>
+      <c r="F2" s="148"/>
+      <c r="G2" s="149"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
@@ -2430,8 +2495,8 @@
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>313</v>
+      <c r="G7" s="160" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -2459,7 +2524,9 @@
       <c r="D9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="10" spans="2:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -2508,19 +2575,19 @@
       <c r="K13" s="9"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="147" t="s">
+      <c r="B14" s="150" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="141" t="s">
+      <c r="C14" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="141" t="s">
+      <c r="D14" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="141" t="s">
+      <c r="E14" s="144" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="141" t="s">
+      <c r="F14" s="144" t="s">
         <v>22</v>
       </c>
       <c r="G14" s="10"/>
@@ -2530,11 +2597,11 @@
       <c r="K14" s="10"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="148"/>
-      <c r="C15" s="142"/>
-      <c r="D15" s="142"/>
-      <c r="E15" s="142"/>
-      <c r="F15" s="142"/>
+      <c r="B15" s="151"/>
+      <c r="C15" s="145"/>
+      <c r="D15" s="145"/>
+      <c r="E15" s="145"/>
+      <c r="F15" s="145"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
@@ -2642,7 +2709,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F21" s="141" t="str">
+      <c r="F21" s="144" t="str">
         <f>IF(ROUNDUP(E21,2)&lt;60%,"C",IF(ROUNDUP(E21,2)&lt;70%,"C+",IF(ROUNDUP(E21,2)&lt;80%,"B",IF(ROUNDUP(E21,2)&lt;90%,"B+",IF(ROUNDUP(E21,2)&lt;100%,"A","A+")))))</f>
         <v>A+</v>
       </c>
@@ -2651,13 +2718,13 @@
       <c r="B22" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="143" t="str">
+      <c r="C22" s="146" t="str">
         <f>VLOOKUP($F$21,$C$27:$D$33,2,FALSE)</f>
         <v>Excellent</v>
       </c>
-      <c r="D22" s="143"/>
-      <c r="E22" s="143"/>
-      <c r="F22" s="142"/>
+      <c r="D22" s="146"/>
+      <c r="E22" s="146"/>
+      <c r="F22" s="145"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="19" t="s">
@@ -5579,12 +5646,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D599F91-A01D-4D1C-B538-B94856059891}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" style="140" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" style="140" customWidth="1"/>
     <col min="2" max="2" width="27.6640625" style="140" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" style="140" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" style="140" customWidth="1"/>
     <col min="4" max="4" width="9.88671875" style="140" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.88671875" style="140" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="30.6640625" style="140" customWidth="1"/>
@@ -5611,94 +5678,97 @@
     <col min="29" max="16384" width="9.109375" style="140"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="139" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+    <row r="1" spans="1:29" s="139" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="141" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1" s="99" t="s">
         <v>219</v>
       </c>
-      <c r="B1" s="99" t="s">
+      <c r="C1" s="99" t="s">
         <v>220</v>
       </c>
-      <c r="C1" s="99" t="s">
+      <c r="D1" s="99" t="s">
         <v>221</v>
       </c>
-      <c r="D1" s="99" t="s">
+      <c r="E1" s="99" t="s">
         <v>222</v>
       </c>
-      <c r="E1" s="99" t="s">
+      <c r="F1" s="99" t="s">
         <v>223</v>
       </c>
-      <c r="F1" s="99" t="s">
+      <c r="G1" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="99" t="s">
+      <c r="H1" s="99" t="s">
         <v>224</v>
       </c>
-      <c r="H1" s="99" t="s">
+      <c r="I1" s="99" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="J1" s="99" t="s">
         <v>225</v>
       </c>
-      <c r="J1" s="99" t="s">
+      <c r="K1" s="99" t="s">
         <v>226</v>
       </c>
-      <c r="K1" s="99" t="s">
+      <c r="L1" s="99" t="s">
         <v>227</v>
       </c>
-      <c r="L1" s="99" t="s">
+      <c r="M1" s="99" t="s">
         <v>228</v>
       </c>
-      <c r="M1" s="99" t="s">
+      <c r="N1" s="99" t="s">
         <v>229</v>
       </c>
-      <c r="N1" s="99" t="s">
+      <c r="O1" s="99" t="s">
         <v>230</v>
       </c>
-      <c r="O1" s="99" t="s">
+      <c r="P1" s="99" t="s">
         <v>231</v>
       </c>
-      <c r="P1" s="99" t="s">
+      <c r="Q1" s="99" t="s">
         <v>232</v>
       </c>
-      <c r="Q1" s="99" t="s">
+      <c r="R1" s="99" t="s">
         <v>233</v>
       </c>
-      <c r="R1" s="99" t="s">
+      <c r="S1" s="99" t="s">
         <v>234</v>
       </c>
-      <c r="S1" s="99" t="s">
+      <c r="T1" s="99" t="s">
         <v>235</v>
       </c>
-      <c r="T1" s="99" t="s">
+      <c r="U1" s="99" t="s">
         <v>236</v>
       </c>
-      <c r="U1" s="99" t="s">
+      <c r="V1" s="99" t="s">
         <v>237</v>
       </c>
-      <c r="V1" s="99" t="s">
+      <c r="W1" s="99" t="s">
         <v>238</v>
       </c>
-      <c r="W1" s="99" t="s">
+      <c r="X1" s="99" t="s">
         <v>239</v>
       </c>
-      <c r="X1" s="99" t="s">
+      <c r="Y1" s="99" t="s">
         <v>240</v>
       </c>
-      <c r="Y1" s="99" t="s">
+      <c r="Z1" s="99" t="s">
         <v>241</v>
       </c>
-      <c r="Z1" s="99" t="s">
+      <c r="AA1" s="99" t="s">
         <v>242</v>
       </c>
-      <c r="AA1" s="99" t="s">
+      <c r="AB1" s="99" t="s">
         <v>243</v>
       </c>
-      <c r="AB1" s="99" t="s">
+      <c r="AC1" s="99" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="22"/>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A2" s="142"/>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -5726,9 +5796,10 @@
       <c r="Z2" s="22"/>
       <c r="AA2" s="22"/>
       <c r="AB2" s="22"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="22"/>
+      <c r="AC2" s="22"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A3" s="143"/>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
@@ -5756,9 +5827,10 @@
       <c r="Z3" s="22"/>
       <c r="AA3" s="22"/>
       <c r="AB3" s="22"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="22"/>
+      <c r="AC3" s="22"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A4" s="143"/>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
       <c r="D4" s="22"/>
@@ -5786,9 +5858,10 @@
       <c r="Z4" s="22"/>
       <c r="AA4" s="22"/>
       <c r="AB4" s="22"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5" s="22"/>
+      <c r="AC4" s="22"/>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A5" s="143"/>
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -5816,9 +5889,10 @@
       <c r="Z5" s="22"/>
       <c r="AA5" s="22"/>
       <c r="AB5" s="22"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="22"/>
+      <c r="AC5" s="22"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A6" s="143"/>
       <c r="B6" s="22"/>
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
@@ -5846,9 +5920,10 @@
       <c r="Z6" s="22"/>
       <c r="AA6" s="22"/>
       <c r="AB6" s="22"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="22"/>
+      <c r="AC6" s="22"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A7" s="143"/>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
       <c r="D7" s="22"/>
@@ -5876,9 +5951,10 @@
       <c r="Z7" s="22"/>
       <c r="AA7" s="22"/>
       <c r="AB7" s="22"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="22"/>
+      <c r="AC7" s="22"/>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A8" s="143"/>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
@@ -5906,9 +5982,10 @@
       <c r="Z8" s="22"/>
       <c r="AA8" s="22"/>
       <c r="AB8" s="22"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="22"/>
+      <c r="AC8" s="22"/>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A9" s="143"/>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
@@ -5936,9 +6013,10 @@
       <c r="Z9" s="22"/>
       <c r="AA9" s="22"/>
       <c r="AB9" s="22"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="22"/>
+      <c r="AC9" s="22"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A10" s="143"/>
       <c r="B10" s="22"/>
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
@@ -5966,9 +6044,10 @@
       <c r="Z10" s="22"/>
       <c r="AA10" s="22"/>
       <c r="AB10" s="22"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="22"/>
+      <c r="AC10" s="22"/>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A11" s="143"/>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
@@ -5996,9 +6075,10 @@
       <c r="Z11" s="22"/>
       <c r="AA11" s="22"/>
       <c r="AB11" s="22"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="22"/>
+      <c r="AC11" s="22"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A12" s="143"/>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
       <c r="D12" s="22"/>
@@ -6026,9 +6106,10 @@
       <c r="Z12" s="22"/>
       <c r="AA12" s="22"/>
       <c r="AB12" s="22"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="22"/>
+      <c r="AC12" s="22"/>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A13" s="143"/>
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
@@ -6056,9 +6137,10 @@
       <c r="Z13" s="22"/>
       <c r="AA13" s="22"/>
       <c r="AB13" s="22"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="22"/>
+      <c r="AC13" s="22"/>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A14" s="143"/>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
       <c r="D14" s="22"/>
@@ -6086,8 +6168,9 @@
       <c r="Z14" s="22"/>
       <c r="AA14" s="22"/>
       <c r="AB14" s="22"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC14" s="22"/>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="22"/>
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
@@ -6116,8 +6199,9 @@
       <c r="Z15" s="22"/>
       <c r="AA15" s="22"/>
       <c r="AB15" s="22"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC15" s="22"/>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="22"/>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
@@ -6146,6 +6230,7 @@
       <c r="Z16" s="22"/>
       <c r="AA16" s="22"/>
       <c r="AB16" s="22"/>
+      <c r="AC16" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6511,21 +6596,21 @@
       <c r="C3" s="105" t="s">
         <v>262</v>
       </c>
-      <c r="D3" s="149" t="s">
+      <c r="D3" s="152" t="s">
         <v>263</v>
       </c>
-      <c r="E3" s="149"/>
-      <c r="F3" s="150"/>
+      <c r="E3" s="152"/>
+      <c r="F3" s="153"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="151" t="s">
+      <c r="A4" s="154" t="s">
         <v>264</v>
       </c>
-      <c r="B4" s="152"/>
-      <c r="C4" s="152"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="152"/>
-      <c r="F4" s="153"/>
+      <c r="B4" s="155"/>
+      <c r="C4" s="155"/>
+      <c r="D4" s="155"/>
+      <c r="E4" s="155"/>
+      <c r="F4" s="156"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6631,11 +6716,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="154"/>
-      <c r="B4" s="155"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="156"/>
+      <c r="A4" s="157"/>
+      <c r="B4" s="158"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="159"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/templates/YesBank/YesBank_Collection_Template_2026-27.xlsx
+++ b/templates/YesBank/YesBank_Collection_Template_2026-27.xlsx
@@ -2022,6 +2022,9 @@
     <xf numFmtId="0" fontId="16" fillId="6" borderId="7" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2071,9 +2074,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -2448,14 +2448,14 @@
   <sheetData>
     <row r="1" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="147" t="s">
+      <c r="B2" s="148" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="148"/>
-      <c r="D2" s="148"/>
-      <c r="E2" s="148"/>
-      <c r="F2" s="148"/>
-      <c r="G2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="150"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
@@ -2495,7 +2495,7 @@
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="160" t="s">
+      <c r="G7" s="144" t="s">
         <v>314</v>
       </c>
     </row>
@@ -2575,19 +2575,19 @@
       <c r="K13" s="9"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="150" t="s">
+      <c r="B14" s="151" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="144" t="s">
+      <c r="C14" s="145" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="144" t="s">
+      <c r="D14" s="145" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="144" t="s">
+      <c r="E14" s="145" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="144" t="s">
+      <c r="F14" s="145" t="s">
         <v>22</v>
       </c>
       <c r="G14" s="10"/>
@@ -2597,11 +2597,11 @@
       <c r="K14" s="10"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="151"/>
-      <c r="C15" s="145"/>
-      <c r="D15" s="145"/>
-      <c r="E15" s="145"/>
-      <c r="F15" s="145"/>
+      <c r="B15" s="152"/>
+      <c r="C15" s="146"/>
+      <c r="D15" s="146"/>
+      <c r="E15" s="146"/>
+      <c r="F15" s="146"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
@@ -2709,7 +2709,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F21" s="144" t="str">
+      <c r="F21" s="145" t="str">
         <f>IF(ROUNDUP(E21,2)&lt;60%,"C",IF(ROUNDUP(E21,2)&lt;70%,"C+",IF(ROUNDUP(E21,2)&lt;80%,"B",IF(ROUNDUP(E21,2)&lt;90%,"B+",IF(ROUNDUP(E21,2)&lt;100%,"A","A+")))))</f>
         <v>A+</v>
       </c>
@@ -2718,13 +2718,13 @@
       <c r="B22" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="146" t="str">
+      <c r="C22" s="147" t="str">
         <f>VLOOKUP($F$21,$C$27:$D$33,2,FALSE)</f>
         <v>Excellent</v>
       </c>
-      <c r="D22" s="146"/>
-      <c r="E22" s="146"/>
-      <c r="F22" s="145"/>
+      <c r="D22" s="147"/>
+      <c r="E22" s="147"/>
+      <c r="F22" s="146"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="19" t="s">
@@ -6596,21 +6596,21 @@
       <c r="C3" s="105" t="s">
         <v>262</v>
       </c>
-      <c r="D3" s="152" t="s">
+      <c r="D3" s="153" t="s">
         <v>263</v>
       </c>
-      <c r="E3" s="152"/>
-      <c r="F3" s="153"/>
+      <c r="E3" s="153"/>
+      <c r="F3" s="154"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="154" t="s">
+      <c r="A4" s="155" t="s">
         <v>264</v>
       </c>
-      <c r="B4" s="155"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="155"/>
-      <c r="F4" s="156"/>
+      <c r="B4" s="156"/>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="157"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6716,11 +6716,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="157"/>
-      <c r="B4" s="158"/>
-      <c r="C4" s="158"/>
-      <c r="D4" s="158"/>
-      <c r="E4" s="159"/>
+      <c r="A4" s="158"/>
+      <c r="B4" s="159"/>
+      <c r="C4" s="159"/>
+      <c r="D4" s="159"/>
+      <c r="E4" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="1">
